--- a/Excel/MagickaSlotConfig.xlsx
+++ b/Excel/MagickaSlotConfig.xlsx
@@ -1,34 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB718099-9BDF-4D69-9831-C155E0174EAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="MagickaSlotProto" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
-<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
-  <connection id="1" xr16:uid="{00000000-0015-0000-FFFF-FFFF00000000}" name="Item_Template" type="4" refreshedVersion="2" background="1" saveData="1">
-    <webPr xml="1" sourceData="1" parsePre="1" consecutive="1" xl2000="1" url="D:\SVN_Work\S_数据表\XML映射模版\Item_Template.xml" htmlTables="1" htmlFormat="all"/>
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <connection id="1" name="Item_Template" type="4" background="1" refreshedVersion="2" saveData="1">
+    <webPr parsePre="1" consecutive="1" xl2000="1" sourceData="1" xml="1" url="D:\SVN_Work\S_数据表\XML映射模版\Item_Template.xml" htmlFormat="all" htmlTables="1"/>
   </connection>
 </connections>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="276">
   <si>
     <t>c</t>
   </si>
@@ -108,135 +120,718 @@
     <t>string</t>
   </si>
   <si>
+    <t>1级攻击栏位</t>
+  </si>
+  <si>
+    <t>Level 1 Attack Slot</t>
+  </si>
+  <si>
+    <t>1;3000000</t>
+  </si>
+  <si>
+    <t>100403;10@100603;10</t>
+  </si>
+  <si>
+    <t>攻击提升10点;物防提升10点</t>
+  </si>
+  <si>
+    <t>Attack +10; Physical Defense +10</t>
+  </si>
+  <si>
+    <t>2级攻击栏位</t>
+  </si>
+  <si>
+    <t>Level 2 Attack Slot</t>
+  </si>
+  <si>
+    <t>10000180;100@1;1000000</t>
+  </si>
+  <si>
+    <t>100403;25@100603;25</t>
+  </si>
+  <si>
+    <t>攻击提升25点;物防提升25点</t>
+  </si>
+  <si>
+    <t>Attack +25; Physical Defense +25</t>
+  </si>
+  <si>
+    <t>3级攻击栏位</t>
+  </si>
+  <si>
+    <t>Level 3 Attack Slot</t>
+  </si>
+  <si>
+    <t>10000180;150@1;2000000</t>
+  </si>
+  <si>
+    <t>100403;40@100603;40</t>
+  </si>
+  <si>
+    <t>攻击提升40点;物防提升40点</t>
+  </si>
+  <si>
+    <t>Attack +40; Physical Defense +40</t>
+  </si>
+  <si>
+    <t>4级攻击栏位</t>
+  </si>
+  <si>
+    <t>Level 4 Attack Slot</t>
+  </si>
+  <si>
+    <t>10000180;200@1;3000000</t>
+  </si>
+  <si>
+    <t>100403;60@100603;60</t>
+  </si>
+  <si>
+    <t>攻击提升60点;物防提升60点</t>
+  </si>
+  <si>
+    <t>Attack +60; Physical Defense +60</t>
+  </si>
+  <si>
+    <t>5级攻击栏位</t>
+  </si>
+  <si>
+    <t>Level 5 Attack Slot</t>
+  </si>
+  <si>
+    <t>10000180;300@1;4000000</t>
+  </si>
+  <si>
+    <t>100403;90@100603;90</t>
+  </si>
+  <si>
+    <t>攻击提升90点;物防提升90点</t>
+  </si>
+  <si>
+    <t>Attack +90; Physical Defense +90</t>
+  </si>
+  <si>
+    <t>6级攻击栏位</t>
+  </si>
+  <si>
+    <t>Level 6 Attack Slot</t>
+  </si>
+  <si>
+    <t>10000180;450@1;5000000</t>
+  </si>
+  <si>
+    <t>100403;120@100603;120</t>
+  </si>
+  <si>
+    <t>攻击提升120点;物防提升120点</t>
+  </si>
+  <si>
+    <t>Attack +120; Physical Defense +120</t>
+  </si>
+  <si>
+    <t>7级攻击栏位</t>
+  </si>
+  <si>
+    <t>Level 7 Attack Slot</t>
+  </si>
+  <si>
+    <t>10000180;600@1;6000000</t>
+  </si>
+  <si>
+    <t>100403;150@100603;150</t>
+  </si>
+  <si>
+    <t>攻击提升150点;物防提升150点</t>
+  </si>
+  <si>
+    <t>Attack +150; Physical Defense +150</t>
+  </si>
+  <si>
+    <t>8级攻击栏位</t>
+  </si>
+  <si>
+    <t>Level 8 Attack Slot</t>
+  </si>
+  <si>
+    <t>10000180;800@1;7000000</t>
+  </si>
+  <si>
+    <t>100403;180@100603;180</t>
+  </si>
+  <si>
+    <t>攻击提升180点;物防提升180点</t>
+  </si>
+  <si>
+    <t>Attack +180; Physical Defense +180</t>
+  </si>
+  <si>
+    <t>9级攻击栏位</t>
+  </si>
+  <si>
+    <t>Level 9 Attack Slot</t>
+  </si>
+  <si>
+    <t>10000180;1000@1;8500000</t>
+  </si>
+  <si>
+    <t>100403;210@100603;210</t>
+  </si>
+  <si>
+    <t>攻击提升210点;物防提升210点</t>
+  </si>
+  <si>
+    <t>Attack +210; Physical Defense +210</t>
+  </si>
+  <si>
+    <t>10级攻击栏位</t>
+  </si>
+  <si>
+    <t>Level 10 Attack Slot</t>
+  </si>
+  <si>
+    <t>10000180;1200@1;10000000</t>
+  </si>
+  <si>
+    <t>100403;240@100603;240</t>
+  </si>
+  <si>
+    <t>攻击提升240点;物防提升240点</t>
+  </si>
+  <si>
+    <t>Attack +240; Physical Defense +240</t>
+  </si>
+  <si>
+    <t>1;30000000@10000180;1500</t>
+  </si>
+  <si>
+    <t>100403;10@100803;10</t>
+  </si>
+  <si>
+    <t>攻击提升10点;魔防提升10点</t>
+  </si>
+  <si>
+    <t>Attack +10; Magical Defense +10</t>
+  </si>
+  <si>
+    <t>100403;25@100803;25</t>
+  </si>
+  <si>
+    <t>攻击提升25点;魔防提升25点</t>
+  </si>
+  <si>
+    <t>Attack +25; Magical Defense +25</t>
+  </si>
+  <si>
+    <t>100403;40@100803;40</t>
+  </si>
+  <si>
+    <t>攻击提升40点;魔防提升40点</t>
+  </si>
+  <si>
+    <t>Attack +40; Magical Defense +40</t>
+  </si>
+  <si>
+    <t>100403;60@100803;60</t>
+  </si>
+  <si>
+    <t>攻击提升60点;魔防提升60点</t>
+  </si>
+  <si>
+    <t>Attack +60; Magical Defense +60</t>
+  </si>
+  <si>
+    <t>100403;90@100803;90</t>
+  </si>
+  <si>
+    <t>攻击提升90点;魔防提升90点</t>
+  </si>
+  <si>
+    <t>Attack +90; Magical Defense +90</t>
+  </si>
+  <si>
+    <t>100403;120@100803;120</t>
+  </si>
+  <si>
+    <t>攻击提升120点;魔防提升120点</t>
+  </si>
+  <si>
+    <t>Attack +120; Magical Defense +120</t>
+  </si>
+  <si>
+    <t>100403;150@100803;150</t>
+  </si>
+  <si>
+    <t>攻击提升150点;魔防提升150点</t>
+  </si>
+  <si>
+    <t>Attack +150; Magical Defense +150</t>
+  </si>
+  <si>
+    <t>100403;180@100803;180</t>
+  </si>
+  <si>
+    <t>攻击提升180点;魔防提升180点</t>
+  </si>
+  <si>
+    <t>Attack +180; Magical Defense +180</t>
+  </si>
+  <si>
+    <t>100403;210@100803;210</t>
+  </si>
+  <si>
+    <t>攻击提升210点;魔防提升210点</t>
+  </si>
+  <si>
+    <t>Attack +210; Magical Defense +210</t>
+  </si>
+  <si>
+    <t>100403;240@100803;240</t>
+  </si>
+  <si>
+    <t>攻击提升240点;魔防提升240点</t>
+  </si>
+  <si>
+    <t>Attack +240; Magical Defense +240</t>
+  </si>
+  <si>
+    <t>1;20000000@10000180;1000</t>
+  </si>
+  <si>
+    <t>100403;10@100203;25</t>
+  </si>
+  <si>
+    <t>攻击提升10点;血量提升25点</t>
+  </si>
+  <si>
+    <t>Attack +10; HP +25</t>
+  </si>
+  <si>
+    <t>100403;25@100203;62</t>
+  </si>
+  <si>
+    <t>攻击提升25点;血量提升60点</t>
+  </si>
+  <si>
+    <t>Attack +25; HP +60</t>
+  </si>
+  <si>
+    <t>100403;40@100203;100</t>
+  </si>
+  <si>
+    <t>攻击提升40点;血量提升100点</t>
+  </si>
+  <si>
+    <t>Attack +40; HP +100</t>
+  </si>
+  <si>
+    <t>100403;60@100203;150</t>
+  </si>
+  <si>
+    <t>攻击提升60点;血量提升150点</t>
+  </si>
+  <si>
+    <t>Attack +60; HP +150</t>
+  </si>
+  <si>
+    <t>100403;90@100203;225</t>
+  </si>
+  <si>
+    <t>攻击提升90点;血量提升225点</t>
+  </si>
+  <si>
+    <t>Attack +90; HP +225</t>
+  </si>
+  <si>
+    <t>100403;120@100203;300</t>
+  </si>
+  <si>
+    <t>攻击提升120点;血量提升300点</t>
+  </si>
+  <si>
+    <t>Attack +120; HP +300</t>
+  </si>
+  <si>
+    <t>100403;150@100203;375</t>
+  </si>
+  <si>
+    <t>攻击提升150点;血量提升375点</t>
+  </si>
+  <si>
+    <t>Attack +150; HP +375</t>
+  </si>
+  <si>
+    <t>100403;180@100203;450</t>
+  </si>
+  <si>
+    <t>攻击提升180点;血量提升450点</t>
+  </si>
+  <si>
+    <t>Attack +180; HP +450</t>
+  </si>
+  <si>
+    <t>100403;210@100203;525</t>
+  </si>
+  <si>
+    <t>攻击提升210点;血量提升525点</t>
+  </si>
+  <si>
+    <t>Attack +210; HP +525</t>
+  </si>
+  <si>
+    <t>100403;240@100203;600</t>
+  </si>
+  <si>
+    <t>攻击提升240点;血量提升600点</t>
+  </si>
+  <si>
+    <t>Attack +240; HP +600</t>
+  </si>
+  <si>
+    <t>1级防护栏位</t>
+  </si>
+  <si>
+    <t>Level 1 Defense Slot</t>
+  </si>
+  <si>
+    <t>1;10000000@10000180;600</t>
+  </si>
+  <si>
+    <t>100203;50</t>
+  </si>
+  <si>
+    <t>血量提升50点</t>
+  </si>
+  <si>
+    <t>HP +50</t>
+  </si>
+  <si>
+    <t>2级防护栏位</t>
+  </si>
+  <si>
+    <t>Level 2 Defense Slot</t>
+  </si>
+  <si>
+    <t>100203;125</t>
+  </si>
+  <si>
+    <t>血量提升125点</t>
+  </si>
+  <si>
+    <t>HP +125</t>
+  </si>
+  <si>
+    <t>3级防护栏位</t>
+  </si>
+  <si>
+    <t>Level 3 Defense Slot</t>
+  </si>
+  <si>
+    <t>100203;200</t>
+  </si>
+  <si>
+    <t>血量提升200点</t>
+  </si>
+  <si>
+    <t>HP +200</t>
+  </si>
+  <si>
+    <t>4级防护栏位</t>
+  </si>
+  <si>
+    <t>Level 4 Defense Slot</t>
+  </si>
+  <si>
+    <t>100203;300</t>
+  </si>
+  <si>
+    <t>血量提升300点</t>
+  </si>
+  <si>
+    <t>HP +300</t>
+  </si>
+  <si>
+    <t>5级防护栏位</t>
+  </si>
+  <si>
+    <t>Level 5 Defense Slot</t>
+  </si>
+  <si>
+    <t>100203;450</t>
+  </si>
+  <si>
+    <t>血量提升450点</t>
+  </si>
+  <si>
+    <t>HP +450</t>
+  </si>
+  <si>
+    <t>6级防护栏位</t>
+  </si>
+  <si>
+    <t>Level 6 Defense Slot</t>
+  </si>
+  <si>
+    <t>100203;600</t>
+  </si>
+  <si>
+    <t>血量提升600点</t>
+  </si>
+  <si>
+    <t>HP +600</t>
+  </si>
+  <si>
+    <t>7级防护栏位</t>
+  </si>
+  <si>
+    <t>Level 7 Defense Slot</t>
+  </si>
+  <si>
+    <t>100203;750</t>
+  </si>
+  <si>
+    <t>血量提升750点</t>
+  </si>
+  <si>
+    <t>HP +750</t>
+  </si>
+  <si>
+    <t>8级防护栏位</t>
+  </si>
+  <si>
+    <t>Level 8 Defense Slot</t>
+  </si>
+  <si>
+    <t>100203;900</t>
+  </si>
+  <si>
+    <t>血量提升900点</t>
+  </si>
+  <si>
+    <t>HP +900</t>
+  </si>
+  <si>
+    <t>9级防护栏位</t>
+  </si>
+  <si>
+    <t>Level 9 Defense Slot</t>
+  </si>
+  <si>
+    <t>100203;1050</t>
+  </si>
+  <si>
+    <t>血量提升1050点</t>
+  </si>
+  <si>
+    <t>HP +1050</t>
+  </si>
+  <si>
+    <t>10级防护栏位</t>
+  </si>
+  <si>
+    <t>Level 10 Defense Slot</t>
+  </si>
+  <si>
+    <t>100203;1200</t>
+  </si>
+  <si>
+    <t>血量提升1200点</t>
+  </si>
+  <si>
+    <t>HP +1200</t>
+  </si>
+  <si>
+    <t>1;5000000@10000180;300</t>
+  </si>
+  <si>
+    <t>101003;10@100203;25</t>
+  </si>
+  <si>
+    <t>魔法提升10点;血量提升25点</t>
+  </si>
+  <si>
+    <t>Magic +10; HP +25</t>
+  </si>
+  <si>
+    <t>101003;25@100203;60</t>
+  </si>
+  <si>
+    <t>魔法提升25点;血量提升60点</t>
+  </si>
+  <si>
+    <t>Magic +25; HP +60</t>
+  </si>
+  <si>
+    <t>101003;40@100203;100</t>
+  </si>
+  <si>
+    <t>魔法提升40点;血量提升100点</t>
+  </si>
+  <si>
+    <t>Magic +40; HP +100</t>
+  </si>
+  <si>
+    <t>101003;60@100203;150</t>
+  </si>
+  <si>
+    <t>魔法提升60点;血量提升150点</t>
+  </si>
+  <si>
+    <t>Magic +60; HP +150</t>
+  </si>
+  <si>
+    <t>101003;90@100203;225</t>
+  </si>
+  <si>
+    <t>魔法提升90点;血量提升225点</t>
+  </si>
+  <si>
+    <t>Magic +90; HP +225</t>
+  </si>
+  <si>
+    <t>101003;120@100203;300</t>
+  </si>
+  <si>
+    <t>魔法提升120点;血量提升300点</t>
+  </si>
+  <si>
+    <t>Magic +120; HP +300</t>
+  </si>
+  <si>
+    <t>101003;150@100203;375</t>
+  </si>
+  <si>
+    <t>魔法提升150点;血量提升375点</t>
+  </si>
+  <si>
+    <t>Magic +150; HP +375</t>
+  </si>
+  <si>
+    <t>101003;180@100203;450</t>
+  </si>
+  <si>
+    <t>魔法提升180点;血量提升450点</t>
+  </si>
+  <si>
+    <t>Magic +180; HP +450</t>
+  </si>
+  <si>
+    <t>101003;210@100203;525</t>
+  </si>
+  <si>
+    <t>魔法提升210点;血量提升525点</t>
+  </si>
+  <si>
+    <t>Magic +210; HP +525</t>
+  </si>
+  <si>
+    <t>101003;240@100203;600</t>
+  </si>
+  <si>
+    <t>魔法提升240点;血量提升600点</t>
+  </si>
+  <si>
+    <t>Magic +240; HP +600</t>
+  </si>
+  <si>
+    <t>1;50000000@10000180;2000</t>
+  </si>
+  <si>
+    <t>100203;25@100603;5@100803;5</t>
+  </si>
+  <si>
+    <t>血量提升25点;物防和魔防提升5点</t>
+  </si>
+  <si>
+    <t>HP +25; All Defense +5</t>
+  </si>
+  <si>
+    <t>100203;60@100603;10@100803;10</t>
+  </si>
+  <si>
+    <t>血量提升60点;物防和魔防提升10点</t>
+  </si>
+  <si>
+    <t>HP +60; All Defense +10</t>
+  </si>
+  <si>
+    <t>100203;100@100603;15@100803;15</t>
+  </si>
+  <si>
+    <t>血量提升100点;物防和魔防提升15点</t>
+  </si>
+  <si>
+    <t>HP +100;All Defense +15</t>
+  </si>
+  <si>
+    <t>100203;150@100603;20@100803;20</t>
+  </si>
+  <si>
+    <t>血量提升150点;物防和魔防提升20点</t>
+  </si>
+  <si>
+    <t>HP +150;All Defense +20</t>
+  </si>
+  <si>
+    <t>100203;225@100603;30@100803;30</t>
+  </si>
+  <si>
+    <t>血量提升225点;物防和魔防提升30点</t>
+  </si>
+  <si>
+    <t>HP +225;All Defense +30</t>
+  </si>
+  <si>
+    <t>100203;300@100603;40@100803;40</t>
+  </si>
+  <si>
+    <t>血量提升300点;物防和魔防提升40点</t>
+  </si>
+  <si>
+    <t>HP +300;All Defense +40</t>
+  </si>
+  <si>
+    <t>100203;375@100603;50@100803;50</t>
+  </si>
+  <si>
+    <t>血量提升375点;物防和魔防提升50点</t>
+  </si>
+  <si>
+    <t>HP +375;All Defense +50</t>
+  </si>
+  <si>
+    <t>100203;450@100603;60@100803;60</t>
+  </si>
+  <si>
+    <t>血量提升450点;物防和魔防提升60点</t>
+  </si>
+  <si>
+    <t>HP +450;All Defense +60</t>
+  </si>
+  <si>
+    <t>100203;525@100603;70@100803;70</t>
+  </si>
+  <si>
+    <t>血量提升525点;物防和魔防提升70点</t>
+  </si>
+  <si>
+    <t>HP +525;All Defense +70</t>
+  </si>
+  <si>
+    <t>100203;600@100603;80@100803;80</t>
+  </si>
+  <si>
+    <t>血量提升600点;物防和魔防提升80点</t>
+  </si>
+  <si>
+    <t>HP +600;All Defense +80</t>
+  </si>
+  <si>
+    <t>1级全能栏位</t>
+  </si>
+  <si>
+    <t>Level 1 All-Round Slot</t>
+  </si>
+  <si>
     <t>10000181;1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>1;30000000@10000180;1500</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>1;5000000@10000180;300</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>1;20000000@10000180;1000</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>1;50000000@10000180;2000</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>1;10000000@10000180;600</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>1;3000000</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>10000180;100@1;1000000</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>10000180;150@1;2000000</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>10000180;200@1;3000000</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>10000180;300@1;4000000</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>10000180;450@1;5000000</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>10000180;600@1;6000000</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>10000180;800@1;7000000</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>10000180;1000@1;8500000</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>10000180;1200@1;10000000</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>1级攻击栏位</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>2级攻击栏位</t>
-  </si>
-  <si>
-    <t>3级攻击栏位</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>4级攻击栏位</t>
-  </si>
-  <si>
-    <t>5级攻击栏位</t>
-  </si>
-  <si>
-    <t>6级攻击栏位</t>
-  </si>
-  <si>
-    <t>7级攻击栏位</t>
-  </si>
-  <si>
-    <t>8级攻击栏位</t>
-  </si>
-  <si>
-    <t>9级攻击栏位</t>
-  </si>
-  <si>
-    <t>10级攻击栏位</t>
-  </si>
-  <si>
-    <t>1级防护栏位</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>2级防护栏位</t>
-  </si>
-  <si>
-    <t>3级防护栏位</t>
-  </si>
-  <si>
-    <t>4级防护栏位</t>
-  </si>
-  <si>
-    <t>5级防护栏位</t>
-  </si>
-  <si>
-    <t>6级防护栏位</t>
-  </si>
-  <si>
-    <t>7级防护栏位</t>
-  </si>
-  <si>
-    <t>8级防护栏位</t>
-  </si>
-  <si>
-    <t>9级防护栏位</t>
-  </si>
-  <si>
-    <t>10级防护栏位</t>
-  </si>
-  <si>
-    <t>1级全能栏位</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>2级全能栏位</t>
@@ -266,660 +861,26 @@
     <t>10级全能栏位</t>
   </si>
   <si>
-    <t>Level 1 Attack Slot</t>
-  </si>
-  <si>
-    <t>Level 2 Attack Slot</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Level 3 Attack Slot</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Level 4 Attack Slot</t>
-  </si>
-  <si>
-    <t>Level 5 Attack Slot</t>
-  </si>
-  <si>
-    <t>Level 6 Attack Slot</t>
-  </si>
-  <si>
-    <t>Level 7 Attack Slot</t>
-  </si>
-  <si>
-    <t>Level 8 Attack Slot</t>
-  </si>
-  <si>
-    <t>Level 9 Attack Slot</t>
-  </si>
-  <si>
-    <t>Level 10 Attack Slot</t>
-  </si>
-  <si>
-    <t>Level 1 Defense Slot</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Level 2 Defense Slot</t>
-  </si>
-  <si>
-    <t>Level 3 Defense Slot</t>
-  </si>
-  <si>
-    <t>Level 4 Defense Slot</t>
-  </si>
-  <si>
-    <t>Level 5 Defense Slot</t>
-  </si>
-  <si>
-    <t>Level 6 Defense Slot</t>
-  </si>
-  <si>
-    <t>Level 7 Defense Slot</t>
-  </si>
-  <si>
-    <t>Level 8 Defense Slot</t>
-  </si>
-  <si>
-    <t>Level 9 Defense Slot</t>
-  </si>
-  <si>
-    <t>Level 10 Defense Slot</t>
-  </si>
-  <si>
-    <t>Level 1 All-Round Slot</t>
-  </si>
-  <si>
-    <t>100403;10@100603;10</t>
-  </si>
-  <si>
-    <t>100403;25@100603;25</t>
-  </si>
-  <si>
-    <t>100403;40@100603;40</t>
-  </si>
-  <si>
-    <t>100403;60@100603;60</t>
-  </si>
-  <si>
-    <t>100403;90@100603;90</t>
-  </si>
-  <si>
-    <t>100403;120@100603;120</t>
-  </si>
-  <si>
-    <t>100403;150@100603;150</t>
-  </si>
-  <si>
-    <t>100403;180@100603;180</t>
-  </si>
-  <si>
-    <t>100403;210@100603;210</t>
-  </si>
-  <si>
-    <t>100403;240@100603;240</t>
-  </si>
-  <si>
-    <t>100403;10@100803;10</t>
-  </si>
-  <si>
-    <t>100403;25@100803;25</t>
-  </si>
-  <si>
-    <t>100403;40@100803;40</t>
-  </si>
-  <si>
-    <t>100403;60@100803;60</t>
-  </si>
-  <si>
-    <t>100403;90@100803;90</t>
-  </si>
-  <si>
-    <t>100403;120@100803;120</t>
-  </si>
-  <si>
-    <t>100403;150@100803;150</t>
-  </si>
-  <si>
-    <t>100403;180@100803;180</t>
-  </si>
-  <si>
-    <t>100403;210@100803;210</t>
-  </si>
-  <si>
-    <t>100403;240@100803;240</t>
-  </si>
-  <si>
-    <t>100403;10@100203;25</t>
-  </si>
-  <si>
-    <t>100403;25@100203;62.5</t>
-  </si>
-  <si>
-    <t>100403;40@100203;100</t>
-  </si>
-  <si>
-    <t>100403;60@100203;150</t>
-  </si>
-  <si>
-    <t>100403;90@100203;225</t>
-  </si>
-  <si>
-    <t>100403;120@100203;300</t>
-  </si>
-  <si>
-    <t>100403;150@100203;375</t>
-  </si>
-  <si>
-    <t>100403;180@100203;450</t>
-  </si>
-  <si>
-    <t>100403;210@100203;525</t>
-  </si>
-  <si>
-    <t>100403;240@100203;600</t>
-  </si>
-  <si>
-    <t>100203;50</t>
-  </si>
-  <si>
-    <t>100203;125</t>
-  </si>
-  <si>
-    <t>100203;200</t>
-  </si>
-  <si>
-    <t>100203;300</t>
-  </si>
-  <si>
-    <t>100203;450</t>
-  </si>
-  <si>
-    <t>100203;600</t>
-  </si>
-  <si>
-    <t>100203;750</t>
-  </si>
-  <si>
-    <t>100203;900</t>
-  </si>
-  <si>
-    <t>100203;1050</t>
-  </si>
-  <si>
-    <t>100203;1200</t>
-  </si>
-  <si>
-    <t>101003;10@100203;25</t>
-  </si>
-  <si>
-    <t>101003;25@100203;60</t>
-  </si>
-  <si>
-    <t>101003;40@100203;100</t>
-  </si>
-  <si>
-    <t>101003;60@100203;150</t>
-  </si>
-  <si>
-    <t>101003;90@100203;225</t>
-  </si>
-  <si>
-    <t>101003;120@100203;300</t>
-  </si>
-  <si>
-    <t>101003;150@100203;375</t>
-  </si>
-  <si>
-    <t>101003;180@100203;450</t>
-  </si>
-  <si>
-    <t>101003;210@100203;525</t>
-  </si>
-  <si>
-    <t>101003;240@100203;600</t>
+    <t>10000181;2</t>
+  </si>
+  <si>
+    <t>10000181;3</t>
   </si>
   <si>
     <t>100403;25@100203;60</t>
-  </si>
-  <si>
-    <t>100203;25@100603;5@100803;5</t>
-  </si>
-  <si>
-    <t>100203;60@100603;10@100803;10</t>
-  </si>
-  <si>
-    <t>100203;100@100603;15@100803;15</t>
-  </si>
-  <si>
-    <t>100203;150@100603;20@100803;20</t>
-  </si>
-  <si>
-    <t>100203;225@100603;30@100803;30</t>
-  </si>
-  <si>
-    <t>100203;300@100603;40@100803;40</t>
-  </si>
-  <si>
-    <t>100203;375@100603;50@100803;50</t>
-  </si>
-  <si>
-    <t>100203;450@100603;60@100803;60</t>
-  </si>
-  <si>
-    <t>100203;525@100603;70@100803;70</t>
-  </si>
-  <si>
-    <t>100203;600@100603;80@100803;80</t>
-  </si>
-  <si>
-    <t>攻击提升10点;物防提升10点</t>
-  </si>
-  <si>
-    <t>攻击提升25点;物防提升25点</t>
-  </si>
-  <si>
-    <t>攻击提升40点;物防提升40点</t>
-  </si>
-  <si>
-    <t>攻击提升60点;物防提升60点</t>
-  </si>
-  <si>
-    <t>攻击提升90点;物防提升90点</t>
-  </si>
-  <si>
-    <t>攻击提升120点;物防提升120点</t>
-  </si>
-  <si>
-    <t>攻击提升150点;物防提升150点</t>
-  </si>
-  <si>
-    <t>攻击提升180点;物防提升180点</t>
-  </si>
-  <si>
-    <t>攻击提升210点;物防提升210点</t>
-  </si>
-  <si>
-    <t>攻击提升240点;物防提升240点</t>
-  </si>
-  <si>
-    <t>攻击提升10点;魔防提升10点</t>
-  </si>
-  <si>
-    <t>攻击提升25点;魔防提升25点</t>
-  </si>
-  <si>
-    <t>攻击提升40点;魔防提升40点</t>
-  </si>
-  <si>
-    <t>攻击提升60点;魔防提升60点</t>
-  </si>
-  <si>
-    <t>攻击提升90点;魔防提升90点</t>
-  </si>
-  <si>
-    <t>攻击提升120点;魔防提升120点</t>
-  </si>
-  <si>
-    <t>攻击提升150点;魔防提升150点</t>
-  </si>
-  <si>
-    <t>攻击提升180点;魔防提升180点</t>
-  </si>
-  <si>
-    <t>攻击提升210点;魔防提升210点</t>
-  </si>
-  <si>
-    <t>攻击提升240点;魔防提升240点</t>
-  </si>
-  <si>
-    <t>攻击提升10点;血量提升25点</t>
-  </si>
-  <si>
-    <t>攻击提升25点;血量提升60点</t>
-  </si>
-  <si>
-    <t>攻击提升40点;血量提升100点</t>
-  </si>
-  <si>
-    <t>攻击提升60点;血量提升150点</t>
-  </si>
-  <si>
-    <t>攻击提升90点;血量提升225点</t>
-  </si>
-  <si>
-    <t>攻击提升120点;血量提升300点</t>
-  </si>
-  <si>
-    <t>攻击提升150点;血量提升375点</t>
-  </si>
-  <si>
-    <t>攻击提升180点;血量提升450点</t>
-  </si>
-  <si>
-    <t>攻击提升210点;血量提升525点</t>
-  </si>
-  <si>
-    <t>攻击提升240点;血量提升600点</t>
-  </si>
-  <si>
-    <t>血量提升50点</t>
-  </si>
-  <si>
-    <t>血量提升125点</t>
-  </si>
-  <si>
-    <t>血量提升200点</t>
-  </si>
-  <si>
-    <t>血量提升300点</t>
-  </si>
-  <si>
-    <t>血量提升450点</t>
-  </si>
-  <si>
-    <t>血量提升600点</t>
-  </si>
-  <si>
-    <t>血量提升750点</t>
-  </si>
-  <si>
-    <t>血量提升900点</t>
-  </si>
-  <si>
-    <t>血量提升1050点</t>
-  </si>
-  <si>
-    <t>血量提升1200点</t>
-  </si>
-  <si>
-    <t>魔法提升10点;血量提升25点</t>
-  </si>
-  <si>
-    <t>魔法提升25点;血量提升60点</t>
-  </si>
-  <si>
-    <t>魔法提升40点;血量提升100点</t>
-  </si>
-  <si>
-    <t>魔法提升60点;血量提升150点</t>
-  </si>
-  <si>
-    <t>魔法提升90点;血量提升225点</t>
-  </si>
-  <si>
-    <t>魔法提升120点;血量提升300点</t>
-  </si>
-  <si>
-    <t>魔法提升150点;血量提升375点</t>
-  </si>
-  <si>
-    <t>魔法提升180点;血量提升450点</t>
-  </si>
-  <si>
-    <t>魔法提升210点;血量提升525点</t>
-  </si>
-  <si>
-    <t>魔法提升240点;血量提升600点</t>
-  </si>
-  <si>
-    <t>Attack +10; Physical Defense +10</t>
-  </si>
-  <si>
-    <t>Attack +25; Physical Defense +25</t>
-  </si>
-  <si>
-    <t>Attack +40; Physical Defense +40</t>
-  </si>
-  <si>
-    <t>Attack +60; Physical Defense +60</t>
-  </si>
-  <si>
-    <t>Attack +90; Physical Defense +90</t>
-  </si>
-  <si>
-    <t>Attack +120; Physical Defense +120</t>
-  </si>
-  <si>
-    <t>Attack +150; Physical Defense +150</t>
-  </si>
-  <si>
-    <t>Attack +180; Physical Defense +180</t>
-  </si>
-  <si>
-    <t>Attack +210; Physical Defense +210</t>
-  </si>
-  <si>
-    <t>Attack +240; Physical Defense +240</t>
-  </si>
-  <si>
-    <t>Attack +10; Magical Defense +10</t>
-  </si>
-  <si>
-    <t>Attack +25; Magical Defense +25</t>
-  </si>
-  <si>
-    <t>Attack +40; Magical Defense +40</t>
-  </si>
-  <si>
-    <t>Attack +60; Magical Defense +60</t>
-  </si>
-  <si>
-    <t>Attack +90; Magical Defense +90</t>
-  </si>
-  <si>
-    <t>Attack +120; Magical Defense +120</t>
-  </si>
-  <si>
-    <t>Attack +150; Magical Defense +150</t>
-  </si>
-  <si>
-    <t>Attack +180; Magical Defense +180</t>
-  </si>
-  <si>
-    <t>Attack +210; Magical Defense +210</t>
-  </si>
-  <si>
-    <t>Attack +240; Magical Defense +240</t>
-  </si>
-  <si>
-    <t>Attack +10; HP +25</t>
-  </si>
-  <si>
-    <t>Attack +25; HP +60</t>
-  </si>
-  <si>
-    <t>Attack +40; HP +100</t>
-  </si>
-  <si>
-    <t>Attack +60; HP +150</t>
-  </si>
-  <si>
-    <t>Attack +90; HP +225</t>
-  </si>
-  <si>
-    <t>Attack +120; HP +300</t>
-  </si>
-  <si>
-    <t>Attack +150; HP +375</t>
-  </si>
-  <si>
-    <t>Attack +180; HP +450</t>
-  </si>
-  <si>
-    <t>Attack +210; HP +525</t>
-  </si>
-  <si>
-    <t>Attack +240; HP +600</t>
-  </si>
-  <si>
-    <t>HP +50</t>
-  </si>
-  <si>
-    <t>HP +125</t>
-  </si>
-  <si>
-    <t>HP +200</t>
-  </si>
-  <si>
-    <t>HP +300</t>
-  </si>
-  <si>
-    <t>HP +450</t>
-  </si>
-  <si>
-    <t>HP +600</t>
-  </si>
-  <si>
-    <t>HP +750</t>
-  </si>
-  <si>
-    <t>HP +900</t>
-  </si>
-  <si>
-    <t>HP +1050</t>
-  </si>
-  <si>
-    <t>HP +1200</t>
-  </si>
-  <si>
-    <t>Magic +10; HP +25</t>
-  </si>
-  <si>
-    <t>Magic +25; HP +60</t>
-  </si>
-  <si>
-    <t>Magic +40; HP +100</t>
-  </si>
-  <si>
-    <t>Magic +60; HP +150</t>
-  </si>
-  <si>
-    <t>Magic +90; HP +225</t>
-  </si>
-  <si>
-    <t>Magic +120; HP +300</t>
-  </si>
-  <si>
-    <t>Magic +150; HP +375</t>
-  </si>
-  <si>
-    <t>Magic +180; HP +450</t>
-  </si>
-  <si>
-    <t>Magic +210; HP +525</t>
-  </si>
-  <si>
-    <t>Magic +240; HP +600</t>
-  </si>
-  <si>
-    <t>血量提升150点;物防和魔防提升20点</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>血量提升25点;物防和魔防提升5点</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>血量提升60点;物防和魔防提升10点</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>血量提升100点;物防和魔防提升15点</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>血量提升225点;物防和魔防提升30点</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>血量提升375点;物防和魔防提升50点</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>血量提升300点;物防和魔防提升40点</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>血量提升450点;物防和魔防提升60点</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>血量提升525点;物防和魔防提升70点</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>血量提升600点;物防和魔防提升80点</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack +10; Physical Defense +10</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>HP +25; All Defense +5</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>HP +60; All Defense +10</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>HP +100;All Defense +15</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>HP +150;All Defense +20</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>HP +225;All Defense +30</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>HP +300;All Defense +40</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>HP +375;All Defense +50</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>HP +450;All Defense +60</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>HP +525;All Defense +70</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>HP +600;All Defense +80</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack +240; Physical Defense +240</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击提升10点;物防提升10点</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>10000181;2</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>10000181;3</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -931,14 +892,12 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -946,33 +905,168 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="48">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -987,7 +1081,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14975432599871821"/>
+        <fgColor theme="0" tint="-0.149754325998718"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -999,78 +1093,264 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79976805932798245"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79976805932798245"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79976805932798245"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79976805932798245"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79976805932798245"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79976805932798245"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799768059327982"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799768059327982"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799768059327982"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799768059327982"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799768059327982"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799768059327982"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -1128,7 +1408,22 @@
         <color theme="1" tint="0.499984740745262"/>
       </top>
       <bottom style="thin">
-        <color theme="4" tint="0.39985351115451523"/>
+        <color theme="4" tint="0.399853511154515"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color theme="1" tint="0.499984740745262"/>
+      </left>
+      <right style="hair">
+        <color theme="1" tint="0.499984740745262"/>
+      </right>
+      <top style="hair">
+        <color theme="1" tint="0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.399975585192419"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1148,949 +1443,1161 @@
       <diagonal/>
     </border>
     <border>
-      <left style="hair">
-        <color theme="1" tint="0.499984740745262"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
       </left>
-      <right style="hair">
-        <color theme="1" tint="0.499984740745262"/>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
       </right>
-      <top style="hair">
-        <color theme="1" tint="0.499984740745262"/>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="313">
+  <cellStyleXfs count="361">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="47" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="47" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="47" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="47" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="47" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="47" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="47" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="47" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="47" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="47" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="47" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="47" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="47" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="47" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="47" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="47" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="47" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="47" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="47" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="47" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2115,345 +2622,413 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="313">
-    <cellStyle name="20% - 强调文字颜色 1 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 2 2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 2 2 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 2 3" xfId="5" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 2 3 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 2 4" xfId="7" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 2 4 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 2 5" xfId="9" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 2 6" xfId="10" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 3" xfId="11" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 3 2" xfId="12" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 3 3" xfId="13" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 4" xfId="14" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 4 2" xfId="15" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 5" xfId="16" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 5 2" xfId="17" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 6" xfId="18" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 7" xfId="19" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 2" xfId="20" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 2 2" xfId="21" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 2 2 2" xfId="22" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 2 2 3" xfId="23" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 2 3" xfId="24" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 2 3 2" xfId="25" xr:uid="{00000000-0005-0000-0000-000049000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 2 4" xfId="26" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 2 4 2" xfId="27" xr:uid="{00000000-0005-0000-0000-00004B000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 2 5" xfId="28" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 2 6" xfId="29" xr:uid="{00000000-0005-0000-0000-00004D000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 3" xfId="30" xr:uid="{00000000-0005-0000-0000-00004E000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 3 2" xfId="31" xr:uid="{00000000-0005-0000-0000-00004F000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 3 3" xfId="32" xr:uid="{00000000-0005-0000-0000-000050000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 4" xfId="33" xr:uid="{00000000-0005-0000-0000-000051000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 4 2" xfId="34" xr:uid="{00000000-0005-0000-0000-000052000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 5" xfId="35" xr:uid="{00000000-0005-0000-0000-000053000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 5 2" xfId="36" xr:uid="{00000000-0005-0000-0000-000054000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 6" xfId="37" xr:uid="{00000000-0005-0000-0000-000055000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 7" xfId="38" xr:uid="{00000000-0005-0000-0000-000056000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 2" xfId="39" xr:uid="{00000000-0005-0000-0000-000057000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 2 2" xfId="40" xr:uid="{00000000-0005-0000-0000-000058000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 2 2 2" xfId="41" xr:uid="{00000000-0005-0000-0000-000059000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 2 2 3" xfId="42" xr:uid="{00000000-0005-0000-0000-00005A000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 2 3" xfId="43" xr:uid="{00000000-0005-0000-0000-00005B000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 2 3 2" xfId="44" xr:uid="{00000000-0005-0000-0000-00005C000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 2 4" xfId="45" xr:uid="{00000000-0005-0000-0000-00005D000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 2 4 2" xfId="46" xr:uid="{00000000-0005-0000-0000-00005E000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 2 5" xfId="47" xr:uid="{00000000-0005-0000-0000-00005F000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 2 6" xfId="48" xr:uid="{00000000-0005-0000-0000-000060000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 3" xfId="49" xr:uid="{00000000-0005-0000-0000-000061000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 3 2" xfId="50" xr:uid="{00000000-0005-0000-0000-000062000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 3 3" xfId="51" xr:uid="{00000000-0005-0000-0000-000063000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 4" xfId="52" xr:uid="{00000000-0005-0000-0000-000064000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 4 2" xfId="53" xr:uid="{00000000-0005-0000-0000-000065000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 5" xfId="54" xr:uid="{00000000-0005-0000-0000-000066000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 5 2" xfId="55" xr:uid="{00000000-0005-0000-0000-000067000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 6" xfId="56" xr:uid="{00000000-0005-0000-0000-000068000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 7" xfId="57" xr:uid="{00000000-0005-0000-0000-000069000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 2" xfId="58" xr:uid="{00000000-0005-0000-0000-00006A000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 2 2" xfId="59" xr:uid="{00000000-0005-0000-0000-00006B000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 2 2 2" xfId="60" xr:uid="{00000000-0005-0000-0000-00006C000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 2 2 3" xfId="61" xr:uid="{00000000-0005-0000-0000-00006D000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 2 3" xfId="62" xr:uid="{00000000-0005-0000-0000-00006E000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 2 3 2" xfId="63" xr:uid="{00000000-0005-0000-0000-00006F000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 2 4" xfId="64" xr:uid="{00000000-0005-0000-0000-000070000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 2 4 2" xfId="65" xr:uid="{00000000-0005-0000-0000-000071000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 2 5" xfId="66" xr:uid="{00000000-0005-0000-0000-000072000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 2 6" xfId="67" xr:uid="{00000000-0005-0000-0000-000073000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 3" xfId="68" xr:uid="{00000000-0005-0000-0000-000074000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 3 2" xfId="69" xr:uid="{00000000-0005-0000-0000-000075000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 3 3" xfId="70" xr:uid="{00000000-0005-0000-0000-000076000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 4" xfId="71" xr:uid="{00000000-0005-0000-0000-000077000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 4 2" xfId="72" xr:uid="{00000000-0005-0000-0000-000078000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 5" xfId="73" xr:uid="{00000000-0005-0000-0000-000079000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 5 2" xfId="74" xr:uid="{00000000-0005-0000-0000-00007A000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 6" xfId="75" xr:uid="{00000000-0005-0000-0000-00007B000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 7" xfId="76" xr:uid="{00000000-0005-0000-0000-00007C000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 2" xfId="77" xr:uid="{00000000-0005-0000-0000-00007D000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 2 2" xfId="78" xr:uid="{00000000-0005-0000-0000-00007E000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 2 2 2" xfId="79" xr:uid="{00000000-0005-0000-0000-00007F000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 2 2 3" xfId="80" xr:uid="{00000000-0005-0000-0000-000080000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 2 3" xfId="81" xr:uid="{00000000-0005-0000-0000-000081000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 2 3 2" xfId="82" xr:uid="{00000000-0005-0000-0000-000082000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 2 4" xfId="83" xr:uid="{00000000-0005-0000-0000-000083000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 2 4 2" xfId="84" xr:uid="{00000000-0005-0000-0000-000084000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 2 5" xfId="85" xr:uid="{00000000-0005-0000-0000-000085000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 2 6" xfId="86" xr:uid="{00000000-0005-0000-0000-000086000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 3" xfId="87" xr:uid="{00000000-0005-0000-0000-000087000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 3 2" xfId="88" xr:uid="{00000000-0005-0000-0000-000088000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 3 3" xfId="89" xr:uid="{00000000-0005-0000-0000-000089000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 4" xfId="90" xr:uid="{00000000-0005-0000-0000-00008A000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 4 2" xfId="91" xr:uid="{00000000-0005-0000-0000-00008B000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 5" xfId="92" xr:uid="{00000000-0005-0000-0000-00008C000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 5 2" xfId="93" xr:uid="{00000000-0005-0000-0000-00008D000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 6" xfId="94" xr:uid="{00000000-0005-0000-0000-00008E000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 7" xfId="95" xr:uid="{00000000-0005-0000-0000-00008F000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 2" xfId="96" xr:uid="{00000000-0005-0000-0000-000090000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 2 2" xfId="97" xr:uid="{00000000-0005-0000-0000-000091000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 2 2 2" xfId="98" xr:uid="{00000000-0005-0000-0000-000092000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 2 2 3" xfId="99" xr:uid="{00000000-0005-0000-0000-000093000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 2 3" xfId="100" xr:uid="{00000000-0005-0000-0000-000094000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 2 3 2" xfId="101" xr:uid="{00000000-0005-0000-0000-000095000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 2 4" xfId="102" xr:uid="{00000000-0005-0000-0000-000096000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 2 4 2" xfId="103" xr:uid="{00000000-0005-0000-0000-000097000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 2 5" xfId="104" xr:uid="{00000000-0005-0000-0000-000098000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 2 6" xfId="105" xr:uid="{00000000-0005-0000-0000-000099000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 3" xfId="106" xr:uid="{00000000-0005-0000-0000-00009A000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 3 2" xfId="107" xr:uid="{00000000-0005-0000-0000-00009B000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 3 3" xfId="108" xr:uid="{00000000-0005-0000-0000-00009C000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 4" xfId="109" xr:uid="{00000000-0005-0000-0000-00009D000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 4 2" xfId="110" xr:uid="{00000000-0005-0000-0000-00009E000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 5" xfId="111" xr:uid="{00000000-0005-0000-0000-00009F000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 5 2" xfId="112" xr:uid="{00000000-0005-0000-0000-0000A0000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 6" xfId="113" xr:uid="{00000000-0005-0000-0000-0000A1000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 7" xfId="114" xr:uid="{00000000-0005-0000-0000-0000A2000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 2" xfId="115" xr:uid="{00000000-0005-0000-0000-0000A3000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 2 2" xfId="116" xr:uid="{00000000-0005-0000-0000-0000A4000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 2 2 2" xfId="117" xr:uid="{00000000-0005-0000-0000-0000A5000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 2 2 3" xfId="118" xr:uid="{00000000-0005-0000-0000-0000A6000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 2 3" xfId="119" xr:uid="{00000000-0005-0000-0000-0000A7000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 2 3 2" xfId="120" xr:uid="{00000000-0005-0000-0000-0000A8000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 2 4" xfId="121" xr:uid="{00000000-0005-0000-0000-0000A9000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 2 4 2" xfId="122" xr:uid="{00000000-0005-0000-0000-0000AA000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 2 5" xfId="123" xr:uid="{00000000-0005-0000-0000-0000AB000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 2 6" xfId="124" xr:uid="{00000000-0005-0000-0000-0000AC000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 3" xfId="125" xr:uid="{00000000-0005-0000-0000-0000AD000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 3 2" xfId="126" xr:uid="{00000000-0005-0000-0000-0000AE000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 3 3" xfId="127" xr:uid="{00000000-0005-0000-0000-0000AF000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 4" xfId="128" xr:uid="{00000000-0005-0000-0000-0000B0000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 4 2" xfId="129" xr:uid="{00000000-0005-0000-0000-0000B1000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 5" xfId="130" xr:uid="{00000000-0005-0000-0000-0000B2000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 5 2" xfId="131" xr:uid="{00000000-0005-0000-0000-0000B3000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 6" xfId="132" xr:uid="{00000000-0005-0000-0000-0000B4000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 7" xfId="133" xr:uid="{00000000-0005-0000-0000-0000B5000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 2" xfId="134" xr:uid="{00000000-0005-0000-0000-0000B6000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 2 2" xfId="135" xr:uid="{00000000-0005-0000-0000-0000B7000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 2 2 2" xfId="136" xr:uid="{00000000-0005-0000-0000-0000B8000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 2 2 3" xfId="137" xr:uid="{00000000-0005-0000-0000-0000B9000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 2 3" xfId="138" xr:uid="{00000000-0005-0000-0000-0000BA000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 2 3 2" xfId="139" xr:uid="{00000000-0005-0000-0000-0000BB000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 2 4" xfId="140" xr:uid="{00000000-0005-0000-0000-0000BC000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 2 4 2" xfId="141" xr:uid="{00000000-0005-0000-0000-0000BD000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 2 5" xfId="142" xr:uid="{00000000-0005-0000-0000-0000BE000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 2 6" xfId="143" xr:uid="{00000000-0005-0000-0000-0000BF000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 3" xfId="144" xr:uid="{00000000-0005-0000-0000-0000C0000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 3 2" xfId="145" xr:uid="{00000000-0005-0000-0000-0000C1000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 3 3" xfId="146" xr:uid="{00000000-0005-0000-0000-0000C2000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 4" xfId="147" xr:uid="{00000000-0005-0000-0000-0000C3000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 4 2" xfId="148" xr:uid="{00000000-0005-0000-0000-0000C4000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 5" xfId="149" xr:uid="{00000000-0005-0000-0000-0000C5000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 5 2" xfId="150" xr:uid="{00000000-0005-0000-0000-0000C6000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 6" xfId="151" xr:uid="{00000000-0005-0000-0000-0000C7000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 7" xfId="152" xr:uid="{00000000-0005-0000-0000-0000C8000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 2" xfId="153" xr:uid="{00000000-0005-0000-0000-0000C9000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 2 2" xfId="154" xr:uid="{00000000-0005-0000-0000-0000CA000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 2 2 2" xfId="155" xr:uid="{00000000-0005-0000-0000-0000CB000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 2 2 3" xfId="156" xr:uid="{00000000-0005-0000-0000-0000CC000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 2 3" xfId="157" xr:uid="{00000000-0005-0000-0000-0000CD000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 2 3 2" xfId="158" xr:uid="{00000000-0005-0000-0000-0000CE000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 2 4" xfId="159" xr:uid="{00000000-0005-0000-0000-0000CF000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 2 4 2" xfId="160" xr:uid="{00000000-0005-0000-0000-0000D0000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 2 5" xfId="161" xr:uid="{00000000-0005-0000-0000-0000D1000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 2 6" xfId="162" xr:uid="{00000000-0005-0000-0000-0000D2000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 3" xfId="163" xr:uid="{00000000-0005-0000-0000-0000D3000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 3 2" xfId="164" xr:uid="{00000000-0005-0000-0000-0000D4000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 3 3" xfId="165" xr:uid="{00000000-0005-0000-0000-0000D5000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 4" xfId="166" xr:uid="{00000000-0005-0000-0000-0000D6000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 4 2" xfId="167" xr:uid="{00000000-0005-0000-0000-0000D7000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 5" xfId="168" xr:uid="{00000000-0005-0000-0000-0000D8000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 5 2" xfId="169" xr:uid="{00000000-0005-0000-0000-0000D9000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 6" xfId="170" xr:uid="{00000000-0005-0000-0000-0000DA000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 7" xfId="171" xr:uid="{00000000-0005-0000-0000-0000DB000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 2" xfId="172" xr:uid="{00000000-0005-0000-0000-0000DC000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 2 2" xfId="173" xr:uid="{00000000-0005-0000-0000-0000DD000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 2 2 2" xfId="174" xr:uid="{00000000-0005-0000-0000-0000DE000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 2 2 3" xfId="175" xr:uid="{00000000-0005-0000-0000-0000DF000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 2 3" xfId="176" xr:uid="{00000000-0005-0000-0000-0000E0000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 2 3 2" xfId="177" xr:uid="{00000000-0005-0000-0000-0000E1000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 2 4" xfId="178" xr:uid="{00000000-0005-0000-0000-0000E2000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 2 4 2" xfId="179" xr:uid="{00000000-0005-0000-0000-0000E3000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 2 5" xfId="180" xr:uid="{00000000-0005-0000-0000-0000E4000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 2 6" xfId="181" xr:uid="{00000000-0005-0000-0000-0000E5000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 3" xfId="182" xr:uid="{00000000-0005-0000-0000-0000E6000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 3 2" xfId="183" xr:uid="{00000000-0005-0000-0000-0000E7000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 3 3" xfId="184" xr:uid="{00000000-0005-0000-0000-0000E8000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 4" xfId="185" xr:uid="{00000000-0005-0000-0000-0000E9000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 4 2" xfId="186" xr:uid="{00000000-0005-0000-0000-0000EA000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 5" xfId="187" xr:uid="{00000000-0005-0000-0000-0000EB000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 5 2" xfId="188" xr:uid="{00000000-0005-0000-0000-0000EC000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 6" xfId="189" xr:uid="{00000000-0005-0000-0000-0000ED000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 7" xfId="190" xr:uid="{00000000-0005-0000-0000-0000EE000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 2" xfId="191" xr:uid="{00000000-0005-0000-0000-0000EF000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 2 2" xfId="192" xr:uid="{00000000-0005-0000-0000-0000F0000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 2 2 2" xfId="193" xr:uid="{00000000-0005-0000-0000-0000F1000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 2 2 3" xfId="194" xr:uid="{00000000-0005-0000-0000-0000F2000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 2 3" xfId="195" xr:uid="{00000000-0005-0000-0000-0000F3000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 2 3 2" xfId="196" xr:uid="{00000000-0005-0000-0000-0000F4000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 2 4" xfId="197" xr:uid="{00000000-0005-0000-0000-0000F5000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 2 4 2" xfId="198" xr:uid="{00000000-0005-0000-0000-0000F6000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 2 5" xfId="199" xr:uid="{00000000-0005-0000-0000-0000F7000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 2 6" xfId="200" xr:uid="{00000000-0005-0000-0000-0000F8000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 3" xfId="201" xr:uid="{00000000-0005-0000-0000-0000F9000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 3 2" xfId="202" xr:uid="{00000000-0005-0000-0000-0000FA000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 3 3" xfId="203" xr:uid="{00000000-0005-0000-0000-0000FB000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 4" xfId="204" xr:uid="{00000000-0005-0000-0000-0000FC000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 4 2" xfId="205" xr:uid="{00000000-0005-0000-0000-0000FD000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 5" xfId="206" xr:uid="{00000000-0005-0000-0000-0000FE000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 5 2" xfId="207" xr:uid="{00000000-0005-0000-0000-0000FF000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 6" xfId="208" xr:uid="{00000000-0005-0000-0000-000000010000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 7" xfId="209" xr:uid="{00000000-0005-0000-0000-000001010000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 2" xfId="210" xr:uid="{00000000-0005-0000-0000-000002010000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 2 2" xfId="211" xr:uid="{00000000-0005-0000-0000-000003010000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 2 2 2" xfId="212" xr:uid="{00000000-0005-0000-0000-000004010000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 2 2 3" xfId="213" xr:uid="{00000000-0005-0000-0000-000005010000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 2 3" xfId="214" xr:uid="{00000000-0005-0000-0000-000006010000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 2 3 2" xfId="215" xr:uid="{00000000-0005-0000-0000-000007010000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 2 4" xfId="216" xr:uid="{00000000-0005-0000-0000-000008010000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 2 4 2" xfId="217" xr:uid="{00000000-0005-0000-0000-000009010000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 2 5" xfId="218" xr:uid="{00000000-0005-0000-0000-00000A010000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 2 6" xfId="219" xr:uid="{00000000-0005-0000-0000-00000B010000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 3" xfId="220" xr:uid="{00000000-0005-0000-0000-00000C010000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 3 2" xfId="221" xr:uid="{00000000-0005-0000-0000-00000D010000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 3 3" xfId="222" xr:uid="{00000000-0005-0000-0000-00000E010000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 4" xfId="223" xr:uid="{00000000-0005-0000-0000-00000F010000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 4 2" xfId="224" xr:uid="{00000000-0005-0000-0000-000010010000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 5" xfId="225" xr:uid="{00000000-0005-0000-0000-000011010000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 5 2" xfId="226" xr:uid="{00000000-0005-0000-0000-000012010000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 6" xfId="227" xr:uid="{00000000-0005-0000-0000-000013010000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 7" xfId="228" xr:uid="{00000000-0005-0000-0000-000014010000}"/>
+  <cellStyles count="361">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="229" xr:uid="{00000000-0005-0000-0000-000015010000}"/>
-    <cellStyle name="常规 2 2" xfId="230" xr:uid="{00000000-0005-0000-0000-000016010000}"/>
-    <cellStyle name="常规 2 3" xfId="231" xr:uid="{00000000-0005-0000-0000-000017010000}"/>
-    <cellStyle name="常规 2 3 2" xfId="232" xr:uid="{00000000-0005-0000-0000-000018010000}"/>
-    <cellStyle name="常规 2 3 2 2" xfId="233" xr:uid="{00000000-0005-0000-0000-000019010000}"/>
-    <cellStyle name="常规 2 3 2 2 2" xfId="234" xr:uid="{00000000-0005-0000-0000-00001A010000}"/>
-    <cellStyle name="常规 2 3 2 2 2 2" xfId="235" xr:uid="{00000000-0005-0000-0000-00001B010000}"/>
-    <cellStyle name="常规 2 3 2 2 2 3" xfId="236" xr:uid="{00000000-0005-0000-0000-00001C010000}"/>
-    <cellStyle name="常规 2 3 2 2 3" xfId="237" xr:uid="{00000000-0005-0000-0000-00001D010000}"/>
-    <cellStyle name="常规 2 3 2 2 3 2" xfId="238" xr:uid="{00000000-0005-0000-0000-00001E010000}"/>
-    <cellStyle name="常规 2 3 2 2 4" xfId="239" xr:uid="{00000000-0005-0000-0000-00001F010000}"/>
-    <cellStyle name="常规 2 3 2 2 4 2" xfId="240" xr:uid="{00000000-0005-0000-0000-000020010000}"/>
-    <cellStyle name="常规 2 3 2 2 5" xfId="241" xr:uid="{00000000-0005-0000-0000-000021010000}"/>
-    <cellStyle name="常规 2 3 2 2 6" xfId="242" xr:uid="{00000000-0005-0000-0000-000022010000}"/>
-    <cellStyle name="常规 2 3 2 3" xfId="243" xr:uid="{00000000-0005-0000-0000-000023010000}"/>
-    <cellStyle name="常规 2 3 2 3 2" xfId="244" xr:uid="{00000000-0005-0000-0000-000024010000}"/>
-    <cellStyle name="常规 2 3 2 3 3" xfId="245" xr:uid="{00000000-0005-0000-0000-000025010000}"/>
-    <cellStyle name="常规 2 3 2 4" xfId="246" xr:uid="{00000000-0005-0000-0000-000026010000}"/>
-    <cellStyle name="常规 2 3 2 4 2" xfId="247" xr:uid="{00000000-0005-0000-0000-000027010000}"/>
-    <cellStyle name="常规 2 3 2 5" xfId="248" xr:uid="{00000000-0005-0000-0000-000028010000}"/>
-    <cellStyle name="常规 2 3 2 5 2" xfId="249" xr:uid="{00000000-0005-0000-0000-000029010000}"/>
-    <cellStyle name="常规 2 3 2 6" xfId="250" xr:uid="{00000000-0005-0000-0000-00002A010000}"/>
-    <cellStyle name="常规 2 3 2 7" xfId="251" xr:uid="{00000000-0005-0000-0000-00002B010000}"/>
-    <cellStyle name="常规 2 3 3" xfId="252" xr:uid="{00000000-0005-0000-0000-00002C010000}"/>
-    <cellStyle name="常规 2 3 3 2" xfId="253" xr:uid="{00000000-0005-0000-0000-00002D010000}"/>
-    <cellStyle name="常规 2 3 3 2 2" xfId="254" xr:uid="{00000000-0005-0000-0000-00002E010000}"/>
-    <cellStyle name="常规 2 3 3 2 3" xfId="255" xr:uid="{00000000-0005-0000-0000-00002F010000}"/>
-    <cellStyle name="常规 2 3 3 3" xfId="256" xr:uid="{00000000-0005-0000-0000-000030010000}"/>
-    <cellStyle name="常规 2 3 3 3 2" xfId="257" xr:uid="{00000000-0005-0000-0000-000031010000}"/>
-    <cellStyle name="常规 2 3 3 4" xfId="258" xr:uid="{00000000-0005-0000-0000-000032010000}"/>
-    <cellStyle name="常规 2 3 3 4 2" xfId="259" xr:uid="{00000000-0005-0000-0000-000033010000}"/>
-    <cellStyle name="常规 2 3 3 5" xfId="260" xr:uid="{00000000-0005-0000-0000-000034010000}"/>
-    <cellStyle name="常规 2 3 3 6" xfId="261" xr:uid="{00000000-0005-0000-0000-000035010000}"/>
-    <cellStyle name="常规 2 3 4" xfId="262" xr:uid="{00000000-0005-0000-0000-000036010000}"/>
-    <cellStyle name="常规 2 3 4 2" xfId="263" xr:uid="{00000000-0005-0000-0000-000037010000}"/>
-    <cellStyle name="常规 2 3 4 3" xfId="264" xr:uid="{00000000-0005-0000-0000-000038010000}"/>
-    <cellStyle name="常规 2 3 5" xfId="265" xr:uid="{00000000-0005-0000-0000-000039010000}"/>
-    <cellStyle name="常规 2 3 5 2" xfId="266" xr:uid="{00000000-0005-0000-0000-00003A010000}"/>
-    <cellStyle name="常规 2 3 6" xfId="267" xr:uid="{00000000-0005-0000-0000-00003B010000}"/>
-    <cellStyle name="常规 2 3 6 2" xfId="268" xr:uid="{00000000-0005-0000-0000-00003C010000}"/>
-    <cellStyle name="常规 2 3 7" xfId="269" xr:uid="{00000000-0005-0000-0000-00003D010000}"/>
-    <cellStyle name="常规 2 3 8" xfId="270" xr:uid="{00000000-0005-0000-0000-00003E010000}"/>
-    <cellStyle name="常规 3" xfId="271" xr:uid="{00000000-0005-0000-0000-00003F010000}"/>
-    <cellStyle name="常规 4" xfId="272" xr:uid="{00000000-0005-0000-0000-000040010000}"/>
-    <cellStyle name="常规 5" xfId="273" xr:uid="{00000000-0005-0000-0000-000041010000}"/>
-    <cellStyle name="常规 5 2" xfId="274" xr:uid="{00000000-0005-0000-0000-000042010000}"/>
-    <cellStyle name="常规 5 2 2" xfId="275" xr:uid="{00000000-0005-0000-0000-000043010000}"/>
-    <cellStyle name="常规 5 2 2 2" xfId="276" xr:uid="{00000000-0005-0000-0000-000044010000}"/>
-    <cellStyle name="常规 5 2 2 3" xfId="277" xr:uid="{00000000-0005-0000-0000-000045010000}"/>
-    <cellStyle name="常规 5 2 3" xfId="278" xr:uid="{00000000-0005-0000-0000-000046010000}"/>
-    <cellStyle name="常规 5 2 3 2" xfId="279" xr:uid="{00000000-0005-0000-0000-000047010000}"/>
-    <cellStyle name="常规 5 2 4" xfId="280" xr:uid="{00000000-0005-0000-0000-000048010000}"/>
-    <cellStyle name="常规 5 2 4 2" xfId="281" xr:uid="{00000000-0005-0000-0000-000049010000}"/>
-    <cellStyle name="常规 5 2 5" xfId="282" xr:uid="{00000000-0005-0000-0000-00004A010000}"/>
-    <cellStyle name="常规 5 2 6" xfId="283" xr:uid="{00000000-0005-0000-0000-00004B010000}"/>
-    <cellStyle name="常规 5 3" xfId="284" xr:uid="{00000000-0005-0000-0000-00004C010000}"/>
-    <cellStyle name="常规 5 3 2" xfId="285" xr:uid="{00000000-0005-0000-0000-00004D010000}"/>
-    <cellStyle name="常规 5 3 3" xfId="286" xr:uid="{00000000-0005-0000-0000-00004E010000}"/>
-    <cellStyle name="常规 5 4" xfId="287" xr:uid="{00000000-0005-0000-0000-00004F010000}"/>
-    <cellStyle name="常规 5 4 2" xfId="288" xr:uid="{00000000-0005-0000-0000-000050010000}"/>
-    <cellStyle name="常规 5 5" xfId="289" xr:uid="{00000000-0005-0000-0000-000051010000}"/>
-    <cellStyle name="常规 5 5 2" xfId="290" xr:uid="{00000000-0005-0000-0000-000052010000}"/>
-    <cellStyle name="常规 5 6" xfId="291" xr:uid="{00000000-0005-0000-0000-000053010000}"/>
-    <cellStyle name="常规 5 7" xfId="292" xr:uid="{00000000-0005-0000-0000-000054010000}"/>
-    <cellStyle name="注释 2" xfId="293" xr:uid="{00000000-0005-0000-0000-000055010000}"/>
-    <cellStyle name="注释 2 2" xfId="294" xr:uid="{00000000-0005-0000-0000-000056010000}"/>
-    <cellStyle name="注释 2 2 2" xfId="295" xr:uid="{00000000-0005-0000-0000-000057010000}"/>
-    <cellStyle name="注释 2 2 2 2" xfId="296" xr:uid="{00000000-0005-0000-0000-000058010000}"/>
-    <cellStyle name="注释 2 2 2 3" xfId="297" xr:uid="{00000000-0005-0000-0000-000059010000}"/>
-    <cellStyle name="注释 2 2 3" xfId="298" xr:uid="{00000000-0005-0000-0000-00005A010000}"/>
-    <cellStyle name="注释 2 2 3 2" xfId="299" xr:uid="{00000000-0005-0000-0000-00005B010000}"/>
-    <cellStyle name="注释 2 2 4" xfId="300" xr:uid="{00000000-0005-0000-0000-00005C010000}"/>
-    <cellStyle name="注释 2 2 4 2" xfId="301" xr:uid="{00000000-0005-0000-0000-00005D010000}"/>
-    <cellStyle name="注释 2 2 5" xfId="302" xr:uid="{00000000-0005-0000-0000-00005E010000}"/>
-    <cellStyle name="注释 2 2 6" xfId="303" xr:uid="{00000000-0005-0000-0000-00005F010000}"/>
-    <cellStyle name="注释 2 3" xfId="304" xr:uid="{00000000-0005-0000-0000-000060010000}"/>
-    <cellStyle name="注释 2 3 2" xfId="305" xr:uid="{00000000-0005-0000-0000-000061010000}"/>
-    <cellStyle name="注释 2 3 3" xfId="306" xr:uid="{00000000-0005-0000-0000-000062010000}"/>
-    <cellStyle name="注释 2 4" xfId="307" xr:uid="{00000000-0005-0000-0000-000063010000}"/>
-    <cellStyle name="注释 2 4 2" xfId="308" xr:uid="{00000000-0005-0000-0000-000064010000}"/>
-    <cellStyle name="注释 2 5" xfId="309" xr:uid="{00000000-0005-0000-0000-000065010000}"/>
-    <cellStyle name="注释 2 5 2" xfId="310" xr:uid="{00000000-0005-0000-0000-000066010000}"/>
-    <cellStyle name="注释 2 6" xfId="311" xr:uid="{00000000-0005-0000-0000-000067010000}"/>
-    <cellStyle name="注释 2 7" xfId="312" xr:uid="{00000000-0005-0000-0000-000068010000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="20% - 强调文字颜色 1 2" xfId="49"/>
+    <cellStyle name="20% - 强调文字颜色 1 2 2" xfId="50"/>
+    <cellStyle name="20% - 强调文字颜色 1 2 2 2" xfId="51"/>
+    <cellStyle name="20% - 强调文字颜色 1 2 2 3" xfId="52"/>
+    <cellStyle name="20% - 强调文字颜色 1 2 3" xfId="53"/>
+    <cellStyle name="20% - 强调文字颜色 1 2 3 2" xfId="54"/>
+    <cellStyle name="20% - 强调文字颜色 1 2 4" xfId="55"/>
+    <cellStyle name="20% - 强调文字颜色 1 2 4 2" xfId="56"/>
+    <cellStyle name="20% - 强调文字颜色 1 2 5" xfId="57"/>
+    <cellStyle name="20% - 强调文字颜色 1 2 6" xfId="58"/>
+    <cellStyle name="20% - 强调文字颜色 1 3" xfId="59"/>
+    <cellStyle name="20% - 强调文字颜色 1 3 2" xfId="60"/>
+    <cellStyle name="20% - 强调文字颜色 1 3 3" xfId="61"/>
+    <cellStyle name="20% - 强调文字颜色 1 4" xfId="62"/>
+    <cellStyle name="20% - 强调文字颜色 1 4 2" xfId="63"/>
+    <cellStyle name="20% - 强调文字颜色 1 5" xfId="64"/>
+    <cellStyle name="20% - 强调文字颜色 1 5 2" xfId="65"/>
+    <cellStyle name="20% - 强调文字颜色 1 6" xfId="66"/>
+    <cellStyle name="20% - 强调文字颜色 1 7" xfId="67"/>
+    <cellStyle name="20% - 强调文字颜色 2 2" xfId="68"/>
+    <cellStyle name="20% - 强调文字颜色 2 2 2" xfId="69"/>
+    <cellStyle name="20% - 强调文字颜色 2 2 2 2" xfId="70"/>
+    <cellStyle name="20% - 强调文字颜色 2 2 2 3" xfId="71"/>
+    <cellStyle name="20% - 强调文字颜色 2 2 3" xfId="72"/>
+    <cellStyle name="20% - 强调文字颜色 2 2 3 2" xfId="73"/>
+    <cellStyle name="20% - 强调文字颜色 2 2 4" xfId="74"/>
+    <cellStyle name="20% - 强调文字颜色 2 2 4 2" xfId="75"/>
+    <cellStyle name="20% - 强调文字颜色 2 2 5" xfId="76"/>
+    <cellStyle name="20% - 强调文字颜色 2 2 6" xfId="77"/>
+    <cellStyle name="20% - 强调文字颜色 2 3" xfId="78"/>
+    <cellStyle name="20% - 强调文字颜色 2 3 2" xfId="79"/>
+    <cellStyle name="20% - 强调文字颜色 2 3 3" xfId="80"/>
+    <cellStyle name="20% - 强调文字颜色 2 4" xfId="81"/>
+    <cellStyle name="20% - 强调文字颜色 2 4 2" xfId="82"/>
+    <cellStyle name="20% - 强调文字颜色 2 5" xfId="83"/>
+    <cellStyle name="20% - 强调文字颜色 2 5 2" xfId="84"/>
+    <cellStyle name="20% - 强调文字颜色 2 6" xfId="85"/>
+    <cellStyle name="20% - 强调文字颜色 2 7" xfId="86"/>
+    <cellStyle name="20% - 强调文字颜色 3 2" xfId="87"/>
+    <cellStyle name="20% - 强调文字颜色 3 2 2" xfId="88"/>
+    <cellStyle name="20% - 强调文字颜色 3 2 2 2" xfId="89"/>
+    <cellStyle name="20% - 强调文字颜色 3 2 2 3" xfId="90"/>
+    <cellStyle name="20% - 强调文字颜色 3 2 3" xfId="91"/>
+    <cellStyle name="20% - 强调文字颜色 3 2 3 2" xfId="92"/>
+    <cellStyle name="20% - 强调文字颜色 3 2 4" xfId="93"/>
+    <cellStyle name="20% - 强调文字颜色 3 2 4 2" xfId="94"/>
+    <cellStyle name="20% - 强调文字颜色 3 2 5" xfId="95"/>
+    <cellStyle name="20% - 强调文字颜色 3 2 6" xfId="96"/>
+    <cellStyle name="20% - 强调文字颜色 3 3" xfId="97"/>
+    <cellStyle name="20% - 强调文字颜色 3 3 2" xfId="98"/>
+    <cellStyle name="20% - 强调文字颜色 3 3 3" xfId="99"/>
+    <cellStyle name="20% - 强调文字颜色 3 4" xfId="100"/>
+    <cellStyle name="20% - 强调文字颜色 3 4 2" xfId="101"/>
+    <cellStyle name="20% - 强调文字颜色 3 5" xfId="102"/>
+    <cellStyle name="20% - 强调文字颜色 3 5 2" xfId="103"/>
+    <cellStyle name="20% - 强调文字颜色 3 6" xfId="104"/>
+    <cellStyle name="20% - 强调文字颜色 3 7" xfId="105"/>
+    <cellStyle name="20% - 强调文字颜色 4 2" xfId="106"/>
+    <cellStyle name="20% - 强调文字颜色 4 2 2" xfId="107"/>
+    <cellStyle name="20% - 强调文字颜色 4 2 2 2" xfId="108"/>
+    <cellStyle name="20% - 强调文字颜色 4 2 2 3" xfId="109"/>
+    <cellStyle name="20% - 强调文字颜色 4 2 3" xfId="110"/>
+    <cellStyle name="20% - 强调文字颜色 4 2 3 2" xfId="111"/>
+    <cellStyle name="20% - 强调文字颜色 4 2 4" xfId="112"/>
+    <cellStyle name="20% - 强调文字颜色 4 2 4 2" xfId="113"/>
+    <cellStyle name="20% - 强调文字颜色 4 2 5" xfId="114"/>
+    <cellStyle name="20% - 强调文字颜色 4 2 6" xfId="115"/>
+    <cellStyle name="20% - 强调文字颜色 4 3" xfId="116"/>
+    <cellStyle name="20% - 强调文字颜色 4 3 2" xfId="117"/>
+    <cellStyle name="20% - 强调文字颜色 4 3 3" xfId="118"/>
+    <cellStyle name="20% - 强调文字颜色 4 4" xfId="119"/>
+    <cellStyle name="20% - 强调文字颜色 4 4 2" xfId="120"/>
+    <cellStyle name="20% - 强调文字颜色 4 5" xfId="121"/>
+    <cellStyle name="20% - 强调文字颜色 4 5 2" xfId="122"/>
+    <cellStyle name="20% - 强调文字颜色 4 6" xfId="123"/>
+    <cellStyle name="20% - 强调文字颜色 4 7" xfId="124"/>
+    <cellStyle name="20% - 强调文字颜色 5 2" xfId="125"/>
+    <cellStyle name="20% - 强调文字颜色 5 2 2" xfId="126"/>
+    <cellStyle name="20% - 强调文字颜色 5 2 2 2" xfId="127"/>
+    <cellStyle name="20% - 强调文字颜色 5 2 2 3" xfId="128"/>
+    <cellStyle name="20% - 强调文字颜色 5 2 3" xfId="129"/>
+    <cellStyle name="20% - 强调文字颜色 5 2 3 2" xfId="130"/>
+    <cellStyle name="20% - 强调文字颜色 5 2 4" xfId="131"/>
+    <cellStyle name="20% - 强调文字颜色 5 2 4 2" xfId="132"/>
+    <cellStyle name="20% - 强调文字颜色 5 2 5" xfId="133"/>
+    <cellStyle name="20% - 强调文字颜色 5 2 6" xfId="134"/>
+    <cellStyle name="20% - 强调文字颜色 5 3" xfId="135"/>
+    <cellStyle name="20% - 强调文字颜色 5 3 2" xfId="136"/>
+    <cellStyle name="20% - 强调文字颜色 5 3 3" xfId="137"/>
+    <cellStyle name="20% - 强调文字颜色 5 4" xfId="138"/>
+    <cellStyle name="20% - 强调文字颜色 5 4 2" xfId="139"/>
+    <cellStyle name="20% - 强调文字颜色 5 5" xfId="140"/>
+    <cellStyle name="20% - 强调文字颜色 5 5 2" xfId="141"/>
+    <cellStyle name="20% - 强调文字颜色 5 6" xfId="142"/>
+    <cellStyle name="20% - 强调文字颜色 5 7" xfId="143"/>
+    <cellStyle name="20% - 强调文字颜色 6 2" xfId="144"/>
+    <cellStyle name="20% - 强调文字颜色 6 2 2" xfId="145"/>
+    <cellStyle name="20% - 强调文字颜色 6 2 2 2" xfId="146"/>
+    <cellStyle name="20% - 强调文字颜色 6 2 2 3" xfId="147"/>
+    <cellStyle name="20% - 强调文字颜色 6 2 3" xfId="148"/>
+    <cellStyle name="20% - 强调文字颜色 6 2 3 2" xfId="149"/>
+    <cellStyle name="20% - 强调文字颜色 6 2 4" xfId="150"/>
+    <cellStyle name="20% - 强调文字颜色 6 2 4 2" xfId="151"/>
+    <cellStyle name="20% - 强调文字颜色 6 2 5" xfId="152"/>
+    <cellStyle name="20% - 强调文字颜色 6 2 6" xfId="153"/>
+    <cellStyle name="20% - 强调文字颜色 6 3" xfId="154"/>
+    <cellStyle name="20% - 强调文字颜色 6 3 2" xfId="155"/>
+    <cellStyle name="20% - 强调文字颜色 6 3 3" xfId="156"/>
+    <cellStyle name="20% - 强调文字颜色 6 4" xfId="157"/>
+    <cellStyle name="20% - 强调文字颜色 6 4 2" xfId="158"/>
+    <cellStyle name="20% - 强调文字颜色 6 5" xfId="159"/>
+    <cellStyle name="20% - 强调文字颜色 6 5 2" xfId="160"/>
+    <cellStyle name="20% - 强调文字颜色 6 6" xfId="161"/>
+    <cellStyle name="20% - 强调文字颜色 6 7" xfId="162"/>
+    <cellStyle name="40% - 强调文字颜色 1 2" xfId="163"/>
+    <cellStyle name="40% - 强调文字颜色 1 2 2" xfId="164"/>
+    <cellStyle name="40% - 强调文字颜色 1 2 2 2" xfId="165"/>
+    <cellStyle name="40% - 强调文字颜色 1 2 2 3" xfId="166"/>
+    <cellStyle name="40% - 强调文字颜色 1 2 3" xfId="167"/>
+    <cellStyle name="40% - 强调文字颜色 1 2 3 2" xfId="168"/>
+    <cellStyle name="40% - 强调文字颜色 1 2 4" xfId="169"/>
+    <cellStyle name="40% - 强调文字颜色 1 2 4 2" xfId="170"/>
+    <cellStyle name="40% - 强调文字颜色 1 2 5" xfId="171"/>
+    <cellStyle name="40% - 强调文字颜色 1 2 6" xfId="172"/>
+    <cellStyle name="40% - 强调文字颜色 1 3" xfId="173"/>
+    <cellStyle name="40% - 强调文字颜色 1 3 2" xfId="174"/>
+    <cellStyle name="40% - 强调文字颜色 1 3 3" xfId="175"/>
+    <cellStyle name="40% - 强调文字颜色 1 4" xfId="176"/>
+    <cellStyle name="40% - 强调文字颜色 1 4 2" xfId="177"/>
+    <cellStyle name="40% - 强调文字颜色 1 5" xfId="178"/>
+    <cellStyle name="40% - 强调文字颜色 1 5 2" xfId="179"/>
+    <cellStyle name="40% - 强调文字颜色 1 6" xfId="180"/>
+    <cellStyle name="40% - 强调文字颜色 1 7" xfId="181"/>
+    <cellStyle name="40% - 强调文字颜色 2 2" xfId="182"/>
+    <cellStyle name="40% - 强调文字颜色 2 2 2" xfId="183"/>
+    <cellStyle name="40% - 强调文字颜色 2 2 2 2" xfId="184"/>
+    <cellStyle name="40% - 强调文字颜色 2 2 2 3" xfId="185"/>
+    <cellStyle name="40% - 强调文字颜色 2 2 3" xfId="186"/>
+    <cellStyle name="40% - 强调文字颜色 2 2 3 2" xfId="187"/>
+    <cellStyle name="40% - 强调文字颜色 2 2 4" xfId="188"/>
+    <cellStyle name="40% - 强调文字颜色 2 2 4 2" xfId="189"/>
+    <cellStyle name="40% - 强调文字颜色 2 2 5" xfId="190"/>
+    <cellStyle name="40% - 强调文字颜色 2 2 6" xfId="191"/>
+    <cellStyle name="40% - 强调文字颜色 2 3" xfId="192"/>
+    <cellStyle name="40% - 强调文字颜色 2 3 2" xfId="193"/>
+    <cellStyle name="40% - 强调文字颜色 2 3 3" xfId="194"/>
+    <cellStyle name="40% - 强调文字颜色 2 4" xfId="195"/>
+    <cellStyle name="40% - 强调文字颜色 2 4 2" xfId="196"/>
+    <cellStyle name="40% - 强调文字颜色 2 5" xfId="197"/>
+    <cellStyle name="40% - 强调文字颜色 2 5 2" xfId="198"/>
+    <cellStyle name="40% - 强调文字颜色 2 6" xfId="199"/>
+    <cellStyle name="40% - 强调文字颜色 2 7" xfId="200"/>
+    <cellStyle name="40% - 强调文字颜色 3 2" xfId="201"/>
+    <cellStyle name="40% - 强调文字颜色 3 2 2" xfId="202"/>
+    <cellStyle name="40% - 强调文字颜色 3 2 2 2" xfId="203"/>
+    <cellStyle name="40% - 强调文字颜色 3 2 2 3" xfId="204"/>
+    <cellStyle name="40% - 强调文字颜色 3 2 3" xfId="205"/>
+    <cellStyle name="40% - 强调文字颜色 3 2 3 2" xfId="206"/>
+    <cellStyle name="40% - 强调文字颜色 3 2 4" xfId="207"/>
+    <cellStyle name="40% - 强调文字颜色 3 2 4 2" xfId="208"/>
+    <cellStyle name="40% - 强调文字颜色 3 2 5" xfId="209"/>
+    <cellStyle name="40% - 强调文字颜色 3 2 6" xfId="210"/>
+    <cellStyle name="40% - 强调文字颜色 3 3" xfId="211"/>
+    <cellStyle name="40% - 强调文字颜色 3 3 2" xfId="212"/>
+    <cellStyle name="40% - 强调文字颜色 3 3 3" xfId="213"/>
+    <cellStyle name="40% - 强调文字颜色 3 4" xfId="214"/>
+    <cellStyle name="40% - 强调文字颜色 3 4 2" xfId="215"/>
+    <cellStyle name="40% - 强调文字颜色 3 5" xfId="216"/>
+    <cellStyle name="40% - 强调文字颜色 3 5 2" xfId="217"/>
+    <cellStyle name="40% - 强调文字颜色 3 6" xfId="218"/>
+    <cellStyle name="40% - 强调文字颜色 3 7" xfId="219"/>
+    <cellStyle name="40% - 强调文字颜色 4 2" xfId="220"/>
+    <cellStyle name="40% - 强调文字颜色 4 2 2" xfId="221"/>
+    <cellStyle name="40% - 强调文字颜色 4 2 2 2" xfId="222"/>
+    <cellStyle name="40% - 强调文字颜色 4 2 2 3" xfId="223"/>
+    <cellStyle name="40% - 强调文字颜色 4 2 3" xfId="224"/>
+    <cellStyle name="40% - 强调文字颜色 4 2 3 2" xfId="225"/>
+    <cellStyle name="40% - 强调文字颜色 4 2 4" xfId="226"/>
+    <cellStyle name="40% - 强调文字颜色 4 2 4 2" xfId="227"/>
+    <cellStyle name="40% - 强调文字颜色 4 2 5" xfId="228"/>
+    <cellStyle name="40% - 强调文字颜色 4 2 6" xfId="229"/>
+    <cellStyle name="40% - 强调文字颜色 4 3" xfId="230"/>
+    <cellStyle name="40% - 强调文字颜色 4 3 2" xfId="231"/>
+    <cellStyle name="40% - 强调文字颜色 4 3 3" xfId="232"/>
+    <cellStyle name="40% - 强调文字颜色 4 4" xfId="233"/>
+    <cellStyle name="40% - 强调文字颜色 4 4 2" xfId="234"/>
+    <cellStyle name="40% - 强调文字颜色 4 5" xfId="235"/>
+    <cellStyle name="40% - 强调文字颜色 4 5 2" xfId="236"/>
+    <cellStyle name="40% - 强调文字颜色 4 6" xfId="237"/>
+    <cellStyle name="40% - 强调文字颜色 4 7" xfId="238"/>
+    <cellStyle name="40% - 强调文字颜色 5 2" xfId="239"/>
+    <cellStyle name="40% - 强调文字颜色 5 2 2" xfId="240"/>
+    <cellStyle name="40% - 强调文字颜色 5 2 2 2" xfId="241"/>
+    <cellStyle name="40% - 强调文字颜色 5 2 2 3" xfId="242"/>
+    <cellStyle name="40% - 强调文字颜色 5 2 3" xfId="243"/>
+    <cellStyle name="40% - 强调文字颜色 5 2 3 2" xfId="244"/>
+    <cellStyle name="40% - 强调文字颜色 5 2 4" xfId="245"/>
+    <cellStyle name="40% - 强调文字颜色 5 2 4 2" xfId="246"/>
+    <cellStyle name="40% - 强调文字颜色 5 2 5" xfId="247"/>
+    <cellStyle name="40% - 强调文字颜色 5 2 6" xfId="248"/>
+    <cellStyle name="40% - 强调文字颜色 5 3" xfId="249"/>
+    <cellStyle name="40% - 强调文字颜色 5 3 2" xfId="250"/>
+    <cellStyle name="40% - 强调文字颜色 5 3 3" xfId="251"/>
+    <cellStyle name="40% - 强调文字颜色 5 4" xfId="252"/>
+    <cellStyle name="40% - 强调文字颜色 5 4 2" xfId="253"/>
+    <cellStyle name="40% - 强调文字颜色 5 5" xfId="254"/>
+    <cellStyle name="40% - 强调文字颜色 5 5 2" xfId="255"/>
+    <cellStyle name="40% - 强调文字颜色 5 6" xfId="256"/>
+    <cellStyle name="40% - 强调文字颜色 5 7" xfId="257"/>
+    <cellStyle name="40% - 强调文字颜色 6 2" xfId="258"/>
+    <cellStyle name="40% - 强调文字颜色 6 2 2" xfId="259"/>
+    <cellStyle name="40% - 强调文字颜色 6 2 2 2" xfId="260"/>
+    <cellStyle name="40% - 强调文字颜色 6 2 2 3" xfId="261"/>
+    <cellStyle name="40% - 强调文字颜色 6 2 3" xfId="262"/>
+    <cellStyle name="40% - 强调文字颜色 6 2 3 2" xfId="263"/>
+    <cellStyle name="40% - 强调文字颜色 6 2 4" xfId="264"/>
+    <cellStyle name="40% - 强调文字颜色 6 2 4 2" xfId="265"/>
+    <cellStyle name="40% - 强调文字颜色 6 2 5" xfId="266"/>
+    <cellStyle name="40% - 强调文字颜色 6 2 6" xfId="267"/>
+    <cellStyle name="40% - 强调文字颜色 6 3" xfId="268"/>
+    <cellStyle name="40% - 强调文字颜色 6 3 2" xfId="269"/>
+    <cellStyle name="40% - 强调文字颜色 6 3 3" xfId="270"/>
+    <cellStyle name="40% - 强调文字颜色 6 4" xfId="271"/>
+    <cellStyle name="40% - 强调文字颜色 6 4 2" xfId="272"/>
+    <cellStyle name="40% - 强调文字颜色 6 5" xfId="273"/>
+    <cellStyle name="40% - 强调文字颜色 6 5 2" xfId="274"/>
+    <cellStyle name="40% - 强调文字颜色 6 6" xfId="275"/>
+    <cellStyle name="40% - 强调文字颜色 6 7" xfId="276"/>
+    <cellStyle name="常规 2" xfId="277"/>
+    <cellStyle name="常规 2 2" xfId="278"/>
+    <cellStyle name="常规 2 3" xfId="279"/>
+    <cellStyle name="常规 2 3 2" xfId="280"/>
+    <cellStyle name="常规 2 3 2 2" xfId="281"/>
+    <cellStyle name="常规 2 3 2 2 2" xfId="282"/>
+    <cellStyle name="常规 2 3 2 2 2 2" xfId="283"/>
+    <cellStyle name="常规 2 3 2 2 2 3" xfId="284"/>
+    <cellStyle name="常规 2 3 2 2 3" xfId="285"/>
+    <cellStyle name="常规 2 3 2 2 3 2" xfId="286"/>
+    <cellStyle name="常规 2 3 2 2 4" xfId="287"/>
+    <cellStyle name="常规 2 3 2 2 4 2" xfId="288"/>
+    <cellStyle name="常规 2 3 2 2 5" xfId="289"/>
+    <cellStyle name="常规 2 3 2 2 6" xfId="290"/>
+    <cellStyle name="常规 2 3 2 3" xfId="291"/>
+    <cellStyle name="常规 2 3 2 3 2" xfId="292"/>
+    <cellStyle name="常规 2 3 2 3 3" xfId="293"/>
+    <cellStyle name="常规 2 3 2 4" xfId="294"/>
+    <cellStyle name="常规 2 3 2 4 2" xfId="295"/>
+    <cellStyle name="常规 2 3 2 5" xfId="296"/>
+    <cellStyle name="常规 2 3 2 5 2" xfId="297"/>
+    <cellStyle name="常规 2 3 2 6" xfId="298"/>
+    <cellStyle name="常规 2 3 2 7" xfId="299"/>
+    <cellStyle name="常规 2 3 3" xfId="300"/>
+    <cellStyle name="常规 2 3 3 2" xfId="301"/>
+    <cellStyle name="常规 2 3 3 2 2" xfId="302"/>
+    <cellStyle name="常规 2 3 3 2 3" xfId="303"/>
+    <cellStyle name="常规 2 3 3 3" xfId="304"/>
+    <cellStyle name="常规 2 3 3 3 2" xfId="305"/>
+    <cellStyle name="常规 2 3 3 4" xfId="306"/>
+    <cellStyle name="常规 2 3 3 4 2" xfId="307"/>
+    <cellStyle name="常规 2 3 3 5" xfId="308"/>
+    <cellStyle name="常规 2 3 3 6" xfId="309"/>
+    <cellStyle name="常规 2 3 4" xfId="310"/>
+    <cellStyle name="常规 2 3 4 2" xfId="311"/>
+    <cellStyle name="常规 2 3 4 3" xfId="312"/>
+    <cellStyle name="常规 2 3 5" xfId="313"/>
+    <cellStyle name="常规 2 3 5 2" xfId="314"/>
+    <cellStyle name="常规 2 3 6" xfId="315"/>
+    <cellStyle name="常规 2 3 6 2" xfId="316"/>
+    <cellStyle name="常规 2 3 7" xfId="317"/>
+    <cellStyle name="常规 2 3 8" xfId="318"/>
+    <cellStyle name="常规 3" xfId="319"/>
+    <cellStyle name="常规 4" xfId="320"/>
+    <cellStyle name="常规 5" xfId="321"/>
+    <cellStyle name="常规 5 2" xfId="322"/>
+    <cellStyle name="常规 5 2 2" xfId="323"/>
+    <cellStyle name="常规 5 2 2 2" xfId="324"/>
+    <cellStyle name="常规 5 2 2 3" xfId="325"/>
+    <cellStyle name="常规 5 2 3" xfId="326"/>
+    <cellStyle name="常规 5 2 3 2" xfId="327"/>
+    <cellStyle name="常规 5 2 4" xfId="328"/>
+    <cellStyle name="常规 5 2 4 2" xfId="329"/>
+    <cellStyle name="常规 5 2 5" xfId="330"/>
+    <cellStyle name="常规 5 2 6" xfId="331"/>
+    <cellStyle name="常规 5 3" xfId="332"/>
+    <cellStyle name="常规 5 3 2" xfId="333"/>
+    <cellStyle name="常规 5 3 3" xfId="334"/>
+    <cellStyle name="常规 5 4" xfId="335"/>
+    <cellStyle name="常规 5 4 2" xfId="336"/>
+    <cellStyle name="常规 5 5" xfId="337"/>
+    <cellStyle name="常规 5 5 2" xfId="338"/>
+    <cellStyle name="常规 5 6" xfId="339"/>
+    <cellStyle name="常规 5 7" xfId="340"/>
+    <cellStyle name="注释 2" xfId="341"/>
+    <cellStyle name="注释 2 2" xfId="342"/>
+    <cellStyle name="注释 2 2 2" xfId="343"/>
+    <cellStyle name="注释 2 2 2 2" xfId="344"/>
+    <cellStyle name="注释 2 2 2 3" xfId="345"/>
+    <cellStyle name="注释 2 2 3" xfId="346"/>
+    <cellStyle name="注释 2 2 3 2" xfId="347"/>
+    <cellStyle name="注释 2 2 4" xfId="348"/>
+    <cellStyle name="注释 2 2 4 2" xfId="349"/>
+    <cellStyle name="注释 2 2 5" xfId="350"/>
+    <cellStyle name="注释 2 2 6" xfId="351"/>
+    <cellStyle name="注释 2 3" xfId="352"/>
+    <cellStyle name="注释 2 3 2" xfId="353"/>
+    <cellStyle name="注释 2 3 3" xfId="354"/>
+    <cellStyle name="注释 2 4" xfId="355"/>
+    <cellStyle name="注释 2 4 2" xfId="356"/>
+    <cellStyle name="注释 2 5" xfId="357"/>
+    <cellStyle name="注释 2 5 2" xfId="358"/>
+    <cellStyle name="注释 2 6" xfId="359"/>
+    <cellStyle name="注释 2 7" xfId="360"/>
   </cellStyles>
   <dxfs count="4">
     <dxf>
       <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="3"/>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="10"/>
         <color theme="1"/>
-        <name val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="none"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="0" tint="-0.14975432599871821"/>
+          <bgColor theme="0" tint="-0.149754325998718"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="3"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0" tint="-0.149754325998718"/>
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center"/>
@@ -2472,27 +3047,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-0.14975432599871821"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
         <i val="0"/>
       </font>
       <fill>
@@ -2512,7 +3067,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{33F73AAB-94A7-4FBD-94B4-D2A5AFC2B6DF}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{C794056D-F40C-450F-AF35-1C7BA448487D}">
       <tableStyleElement type="wholeTable" dxfId="3"/>
       <tableStyleElement type="headerRow" dxfId="2"/>
     </tableStyle>
@@ -2520,9 +3075,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2552,32 +3104,32 @@
     </xsd:schema>
   </Schema>
   <Map ID="1" Name="DateArea_映射" RootElement="DateArea" SchemaID="Schema1" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true">
-    <DataBinding FileBinding="true" ConnectionID="1" DataBindingLoadMode="1"/>
+    <DataBinding ConnectionID="1" FileBinding="true" DataBindingLoadMode="1"/>
   </Map>
 </MapInfo>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表1" displayName="表1" ref="C3:N5" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="C3:N5" totalsRowShown="0">
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id">
+    <tableColumn id="1" name="Id">
       <calculatedColumnFormula>C3+1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="魔能类型"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="位置"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="名字"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="名字2" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="等级">
+    <tableColumn id="5" name="魔能类型"/>
+    <tableColumn id="10" name="位置"/>
+    <tableColumn id="3" name="名字"/>
+    <tableColumn id="8" name="名字2" dataDxfId="0"/>
+    <tableColumn id="4" name="等级">
       <calculatedColumnFormula>H3+1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="开启消耗道具"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="开启需要总等级"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="升级需要经验"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="额外属性"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="额外描述">
+    <tableColumn id="2" name="开启消耗道具"/>
+    <tableColumn id="11" name="开启需要总等级"/>
+    <tableColumn id="12" name="升级需要经验"/>
+    <tableColumn id="6" name="额外属性"/>
+    <tableColumn id="7" name="额外描述">
       <calculatedColumnFormula>"生命上限提升+"&amp;H4&amp;"%,眩晕抵抗概率+"&amp;H4&amp;"%"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="额外描述2" dataDxfId="0"/>
+    <tableColumn id="9" name="额外描述2" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2862,29 +3414,29 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:N95"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="3" max="4" width="21.625" customWidth="1"/>
     <col min="5" max="5" width="15.375" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
     <col min="7" max="7" width="19.875" customWidth="1"/>
     <col min="8" max="8" width="17.375" customWidth="1"/>
-    <col min="9" max="9" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.875" customWidth="1"/>
     <col min="10" max="11" width="19.5" customWidth="1"/>
-    <col min="12" max="12" width="18" style="1" customWidth="1"/>
+    <col min="12" max="12" width="32.5" style="1" customWidth="1"/>
     <col min="13" max="13" width="34" style="1" customWidth="1"/>
     <col min="14" max="14" width="36.125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:14" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" s="1" customFormat="1" ht="20.1" customHeight="1"/>
+    <row r="2" ht="20.1" customHeight="1" spans="3:14">
       <c r="G2" t="s">
         <v>0</v>
       </c>
@@ -2895,7 +3447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C3" s="4" t="s">
         <v>1</v>
       </c>
@@ -2933,7 +3485,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C4" s="4" t="s">
         <v>1</v>
       </c>
@@ -2971,7 +3523,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="3:14" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" s="2" customFormat="1" ht="19.5" customHeight="1" spans="3:14">
       <c r="C5" s="4" t="s">
         <v>24</v>
       </c>
@@ -3009,7 +3561,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C6" s="6">
         <v>1001</v>
       </c>
@@ -3020,16 +3572,16 @@
         <v>1</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="H6" s="6">
         <v>1</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="J6" s="6">
         <v>0</v>
@@ -3038,16 +3590,16 @@
         <v>100</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>93</v>
+        <v>29</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>154</v>
+        <v>30</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="7" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C7" s="6">
         <v>1002</v>
       </c>
@@ -3058,16 +3610,16 @@
         <v>1</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="H7" s="6">
         <v>2</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J7" s="6">
         <v>0</v>
@@ -3076,16 +3628,16 @@
         <v>150</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>155</v>
+        <v>36</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="8" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C8" s="6">
         <v>1003</v>
       </c>
@@ -3096,16 +3648,16 @@
         <v>1</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="H8" s="6">
         <v>3</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="J8" s="6">
         <v>0</v>
@@ -3114,16 +3666,16 @@
         <v>200</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>156</v>
+        <v>42</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="9" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C9" s="6">
         <v>1004</v>
       </c>
@@ -3134,16 +3686,16 @@
         <v>1</v>
       </c>
       <c r="F9" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" s="6" t="s">
         <v>45</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>75</v>
       </c>
       <c r="H9" s="6">
         <v>4</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="J9" s="6">
         <v>0</v>
@@ -3152,16 +3704,16 @@
         <v>300</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>157</v>
+        <v>48</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="10" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C10" s="6">
         <v>1005</v>
       </c>
@@ -3172,16 +3724,16 @@
         <v>1</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="H10" s="6">
         <v>5</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="J10" s="6">
         <v>0</v>
@@ -3190,16 +3742,16 @@
         <v>450</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>158</v>
+        <v>54</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="11" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C11" s="6">
         <v>1006</v>
       </c>
@@ -3210,16 +3762,16 @@
         <v>1</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="H11" s="6">
         <v>6</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="J11" s="6">
         <v>0</v>
@@ -3228,16 +3780,16 @@
         <v>600</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>159</v>
+        <v>60</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="12" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C12" s="6">
         <v>1007</v>
       </c>
@@ -3248,16 +3800,16 @@
         <v>1</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="H12" s="6">
         <v>7</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="J12" s="6">
         <v>0</v>
@@ -3266,16 +3818,16 @@
         <v>800</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>99</v>
+        <v>65</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="13" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C13" s="6">
         <v>1008</v>
       </c>
@@ -3286,16 +3838,16 @@
         <v>1</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="H13" s="6">
         <v>8</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="J13" s="6">
         <v>0</v>
@@ -3304,16 +3856,16 @@
         <v>1000</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>161</v>
+        <v>72</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="14" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C14" s="6">
         <v>1009</v>
       </c>
@@ -3324,16 +3876,16 @@
         <v>1</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H14" s="6">
         <v>9</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="J14" s="6">
         <v>0</v>
@@ -3342,16 +3894,16 @@
         <v>1200</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>162</v>
+        <v>78</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="15" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C15" s="6">
         <v>1010</v>
       </c>
@@ -3362,7 +3914,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>81</v>
@@ -3371,7 +3923,7 @@
         <v>10</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="J15" s="6">
         <v>0</v>
@@ -3380,16 +3932,16 @@
         <v>1500</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>163</v>
+        <v>84</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="16" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C16" s="6">
         <v>2001</v>
       </c>
@@ -3400,16 +3952,16 @@
         <v>2</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="H16" s="6">
         <v>1</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>27</v>
+        <v>86</v>
       </c>
       <c r="J16" s="6">
         <v>12</v>
@@ -3418,16 +3970,16 @@
         <v>100</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>164</v>
+        <v>88</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:14">
       <c r="C17" s="6">
         <v>2002</v>
       </c>
@@ -3438,16 +3990,16 @@
         <v>2</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="H17" s="6">
         <v>2</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J17" s="6">
         <v>12</v>
@@ -3456,16 +4008,16 @@
         <v>150</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>165</v>
+        <v>91</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:14">
       <c r="C18" s="6">
         <v>2003</v>
       </c>
@@ -3476,16 +4028,16 @@
         <v>2</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="H18" s="6">
         <v>3</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="J18" s="6">
         <v>12</v>
@@ -3494,16 +4046,16 @@
         <v>200</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>166</v>
+        <v>94</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:14">
       <c r="C19" s="6">
         <v>2004</v>
       </c>
@@ -3514,16 +4066,16 @@
         <v>2</v>
       </c>
       <c r="F19" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G19" s="6" t="s">
         <v>45</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>75</v>
       </c>
       <c r="H19" s="6">
         <v>4</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="J19" s="6">
         <v>12</v>
@@ -3532,16 +4084,16 @@
         <v>300</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>167</v>
+        <v>97</v>
       </c>
       <c r="N19" s="7" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:14">
       <c r="C20" s="6">
         <v>2005</v>
       </c>
@@ -3552,16 +4104,16 @@
         <v>2</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="H20" s="6">
         <v>5</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="J20" s="6">
         <v>12</v>
@@ -3570,16 +4122,16 @@
         <v>450</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="M20" s="7" t="s">
-        <v>168</v>
+        <v>100</v>
       </c>
       <c r="N20" s="7" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:14">
       <c r="C21" s="6">
         <v>2006</v>
       </c>
@@ -3590,16 +4142,16 @@
         <v>2</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="H21" s="6">
         <v>6</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="J21" s="6">
         <v>12</v>
@@ -3608,16 +4160,16 @@
         <v>600</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>169</v>
+        <v>103</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:14">
       <c r="C22" s="6">
         <v>2007</v>
       </c>
@@ -3628,16 +4180,16 @@
         <v>2</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="H22" s="6">
         <v>7</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="J22" s="6">
         <v>12</v>
@@ -3646,16 +4198,16 @@
         <v>800</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="M22" s="7" t="s">
-        <v>170</v>
+        <v>106</v>
       </c>
       <c r="N22" s="7" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:14">
       <c r="C23" s="6">
         <v>2008</v>
       </c>
@@ -3666,16 +4218,16 @@
         <v>2</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="H23" s="6">
         <v>8</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="J23" s="6">
         <v>12</v>
@@ -3684,16 +4236,16 @@
         <v>1000</v>
       </c>
       <c r="L23" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="N23" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="M23" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="N23" s="7" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="24" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:14">
       <c r="C24" s="6">
         <v>2009</v>
       </c>
@@ -3704,16 +4256,16 @@
         <v>2</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H24" s="6">
         <v>9</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="J24" s="6">
         <v>12</v>
@@ -3725,13 +4277,13 @@
         <v>111</v>
       </c>
       <c r="M24" s="7" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
       <c r="N24" s="7" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:14">
       <c r="C25" s="6">
         <v>2010</v>
       </c>
@@ -3742,7 +4294,7 @@
         <v>2</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>81</v>
@@ -3751,7 +4303,7 @@
         <v>10</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="J25" s="6">
         <v>12</v>
@@ -3760,16 +4312,16 @@
         <v>1500</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M25" s="7" t="s">
-        <v>173</v>
+        <v>115</v>
       </c>
       <c r="N25" s="7" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:14">
       <c r="C26" s="6">
         <v>3001</v>
       </c>
@@ -3780,16 +4332,16 @@
         <v>3</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="H26" s="6">
         <v>1</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>29</v>
+        <v>117</v>
       </c>
       <c r="J26" s="6">
         <v>24</v>
@@ -3798,16 +4350,16 @@
         <v>100</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="M26" s="7" t="s">
-        <v>174</v>
+        <v>119</v>
       </c>
       <c r="N26" s="7" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:14">
       <c r="C27" s="6">
         <v>3002</v>
       </c>
@@ -3818,16 +4370,16 @@
         <v>3</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="H27" s="6">
         <v>2</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J27" s="6">
         <v>24</v>
@@ -3836,16 +4388,16 @@
         <v>150</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="M27" s="7" t="s">
-        <v>175</v>
+        <v>122</v>
       </c>
       <c r="N27" s="7" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:14">
       <c r="C28" s="6">
         <v>3003</v>
       </c>
@@ -3856,16 +4408,16 @@
         <v>3</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="H28" s="6">
         <v>3</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="J28" s="6">
         <v>24</v>
@@ -3874,16 +4426,16 @@
         <v>200</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="M28" s="7" t="s">
-        <v>176</v>
+        <v>125</v>
       </c>
       <c r="N28" s="7" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:14">
       <c r="A29" s="9"/>
       <c r="C29" s="6">
         <v>3004</v>
@@ -3895,16 +4447,16 @@
         <v>3</v>
       </c>
       <c r="F29" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G29" s="6" t="s">
         <v>45</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>75</v>
       </c>
       <c r="H29" s="6">
         <v>4</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="J29" s="6">
         <v>24</v>
@@ -3913,16 +4465,16 @@
         <v>300</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="M29" s="7" t="s">
-        <v>177</v>
+        <v>128</v>
       </c>
       <c r="N29" s="7" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:14">
       <c r="C30" s="6">
         <v>3005</v>
       </c>
@@ -3933,16 +4485,16 @@
         <v>3</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="H30" s="6">
         <v>5</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="J30" s="6">
         <v>24</v>
@@ -3951,16 +4503,16 @@
         <v>450</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="M30" s="7" t="s">
-        <v>178</v>
+        <v>131</v>
       </c>
       <c r="N30" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:14">
       <c r="A31" s="9"/>
       <c r="C31" s="6">
         <v>3006</v>
@@ -3972,16 +4524,16 @@
         <v>3</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="H31" s="6">
         <v>6</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="J31" s="6">
         <v>24</v>
@@ -3990,16 +4542,16 @@
         <v>600</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="M31" s="7" t="s">
-        <v>179</v>
+        <v>134</v>
       </c>
       <c r="N31" s="7" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:14">
       <c r="C32" s="6">
         <v>3007</v>
       </c>
@@ -4010,16 +4562,16 @@
         <v>3</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="H32" s="6">
         <v>7</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="J32" s="6">
         <v>24</v>
@@ -4028,16 +4580,16 @@
         <v>800</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="M32" s="7" t="s">
-        <v>180</v>
+        <v>137</v>
       </c>
       <c r="N32" s="7" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="33" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:14">
       <c r="A33" s="9"/>
       <c r="C33" s="6">
         <v>3008</v>
@@ -4049,16 +4601,16 @@
         <v>3</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="H33" s="6">
         <v>8</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="J33" s="6">
         <v>24</v>
@@ -4067,16 +4619,16 @@
         <v>1000</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="M33" s="7" t="s">
-        <v>181</v>
+        <v>140</v>
       </c>
       <c r="N33" s="7" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="34" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:14">
       <c r="C34" s="6">
         <v>3009</v>
       </c>
@@ -4087,16 +4639,16 @@
         <v>3</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H34" s="6">
         <v>9</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="J34" s="6">
         <v>24</v>
@@ -4105,16 +4657,16 @@
         <v>1200</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="M34" s="7" t="s">
-        <v>182</v>
+        <v>143</v>
       </c>
       <c r="N34" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="35" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:14">
       <c r="A35" s="9"/>
       <c r="C35" s="6">
         <v>3010</v>
@@ -4126,7 +4678,7 @@
         <v>3</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>81</v>
@@ -4135,7 +4687,7 @@
         <v>10</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="J35" s="6">
         <v>24</v>
@@ -4144,16 +4696,16 @@
         <v>1500</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="M35" s="7" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="N35" s="7" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:14">
       <c r="C36" s="6">
         <v>4001</v>
       </c>
@@ -4164,16 +4716,16 @@
         <v>4</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>52</v>
+        <v>148</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="H36" s="6">
         <v>1</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>31</v>
+        <v>150</v>
       </c>
       <c r="J36" s="6">
         <v>5</v>
@@ -4182,16 +4734,16 @@
         <v>100</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="M36" s="7" t="s">
-        <v>184</v>
+        <v>152</v>
       </c>
       <c r="N36" s="7" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="37" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:14">
       <c r="C37" s="6">
         <v>4002</v>
       </c>
@@ -4202,16 +4754,16 @@
         <v>4</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>53</v>
+        <v>154</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>83</v>
+        <v>155</v>
       </c>
       <c r="H37" s="6">
         <v>2</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J37" s="6">
         <v>5</v>
@@ -4220,16 +4772,16 @@
         <v>150</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c r="M37" s="7" t="s">
-        <v>185</v>
+        <v>157</v>
       </c>
       <c r="N37" s="7" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="38" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:14">
       <c r="C38" s="6">
         <v>4003</v>
       </c>
@@ -4240,16 +4792,16 @@
         <v>4</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>54</v>
+        <v>159</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>84</v>
+        <v>160</v>
       </c>
       <c r="H38" s="6">
         <v>3</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="J38" s="6">
         <v>5</v>
@@ -4258,16 +4810,16 @@
         <v>200</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="M38" s="7" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="N38" s="7" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="39" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:14">
       <c r="C39" s="6">
         <v>4004</v>
       </c>
@@ -4278,16 +4830,16 @@
         <v>4</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>55</v>
+        <v>164</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>85</v>
+        <v>165</v>
       </c>
       <c r="H39" s="6">
         <v>4</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="J39" s="6">
         <v>5</v>
@@ -4296,16 +4848,16 @@
         <v>300</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>126</v>
+        <v>166</v>
       </c>
       <c r="M39" s="7" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="N39" s="7" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="40" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:14">
       <c r="C40" s="6">
         <v>4005</v>
       </c>
@@ -4316,16 +4868,16 @@
         <v>4</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>56</v>
+        <v>169</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>86</v>
+        <v>170</v>
       </c>
       <c r="H40" s="6">
         <v>5</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="J40" s="6">
         <v>5</v>
@@ -4334,16 +4886,16 @@
         <v>450</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>127</v>
+        <v>171</v>
       </c>
       <c r="M40" s="7" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="N40" s="7" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="41" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:14">
       <c r="C41" s="6">
         <v>4006</v>
       </c>
@@ -4354,16 +4906,16 @@
         <v>4</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>57</v>
+        <v>174</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>87</v>
+        <v>175</v>
       </c>
       <c r="H41" s="6">
         <v>6</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="J41" s="6">
         <v>5</v>
@@ -4372,16 +4924,16 @@
         <v>600</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>128</v>
+        <v>176</v>
       </c>
       <c r="M41" s="7" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="N41" s="7" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="42" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:14">
       <c r="C42" s="6">
         <v>4007</v>
       </c>
@@ -4392,16 +4944,16 @@
         <v>4</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>88</v>
+        <v>180</v>
       </c>
       <c r="H42" s="6">
         <v>7</v>
       </c>
       <c r="I42" s="8" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="J42" s="6">
         <v>5</v>
@@ -4410,16 +4962,16 @@
         <v>800</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>129</v>
+        <v>181</v>
       </c>
       <c r="M42" s="7" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="N42" s="7" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="43" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:14">
       <c r="C43" s="6">
         <v>4008</v>
       </c>
@@ -4430,16 +4982,16 @@
         <v>4</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>59</v>
+        <v>184</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>89</v>
+        <v>185</v>
       </c>
       <c r="H43" s="6">
         <v>8</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="J43" s="6">
         <v>5</v>
@@ -4448,16 +5000,16 @@
         <v>1000</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>130</v>
+        <v>186</v>
       </c>
       <c r="M43" s="7" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="N43" s="7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="44" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:14">
       <c r="C44" s="6">
         <v>4009</v>
       </c>
@@ -4468,16 +5020,16 @@
         <v>4</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>60</v>
+        <v>189</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="H44" s="6">
         <v>9</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="J44" s="6">
         <v>5</v>
@@ -4486,16 +5038,16 @@
         <v>1200</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>131</v>
+        <v>191</v>
       </c>
       <c r="M44" s="7" t="s">
         <v>192</v>
       </c>
       <c r="N44" s="7" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="45" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:14">
       <c r="C45" s="6">
         <v>4010</v>
       </c>
@@ -4506,16 +5058,16 @@
         <v>4</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>61</v>
+        <v>194</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>91</v>
+        <v>195</v>
       </c>
       <c r="H45" s="6">
         <v>10</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="J45" s="6">
         <v>5</v>
@@ -4524,16 +5076,16 @@
         <v>1500</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>132</v>
+        <v>196</v>
       </c>
       <c r="M45" s="7" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="N45" s="7" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="46" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:14">
       <c r="C46" s="6">
         <v>5001</v>
       </c>
@@ -4544,16 +5096,16 @@
         <v>5</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>52</v>
+        <v>148</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="H46" s="6">
         <v>1</v>
       </c>
       <c r="I46" s="8" t="s">
-        <v>28</v>
+        <v>199</v>
       </c>
       <c r="J46" s="6">
         <v>18</v>
@@ -4562,16 +5114,16 @@
         <v>100</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>133</v>
+        <v>200</v>
       </c>
       <c r="M46" s="7" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="N46" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="47" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:14">
       <c r="C47" s="6">
         <v>5002</v>
       </c>
@@ -4582,16 +5134,16 @@
         <v>5</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>53</v>
+        <v>154</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>83</v>
+        <v>155</v>
       </c>
       <c r="H47" s="6">
         <v>2</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J47" s="6">
         <v>18</v>
@@ -4600,16 +5152,16 @@
         <v>150</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>134</v>
+        <v>203</v>
       </c>
       <c r="M47" s="7" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="N47" s="7" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="48" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:14">
       <c r="C48" s="6">
         <v>5003</v>
       </c>
@@ -4620,16 +5172,16 @@
         <v>5</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>54</v>
+        <v>159</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>84</v>
+        <v>160</v>
       </c>
       <c r="H48" s="6">
         <v>3</v>
       </c>
       <c r="I48" s="8" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="J48" s="6">
         <v>18</v>
@@ -4638,16 +5190,16 @@
         <v>200</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>135</v>
+        <v>206</v>
       </c>
       <c r="M48" s="7" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="N48" s="7" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="49" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="49" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C49" s="6">
         <v>5004</v>
       </c>
@@ -4658,16 +5210,16 @@
         <v>5</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>55</v>
+        <v>164</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>85</v>
+        <v>165</v>
       </c>
       <c r="H49" s="6">
         <v>4</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="J49" s="6">
         <v>18</v>
@@ -4676,16 +5228,16 @@
         <v>300</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>136</v>
+        <v>209</v>
       </c>
       <c r="M49" s="7" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="N49" s="7" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="50" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="50" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C50" s="6">
         <v>5005</v>
       </c>
@@ -4696,16 +5248,16 @@
         <v>5</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>56</v>
+        <v>169</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>86</v>
+        <v>170</v>
       </c>
       <c r="H50" s="6">
         <v>5</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="J50" s="6">
         <v>18</v>
@@ -4714,16 +5266,16 @@
         <v>450</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>137</v>
+        <v>212</v>
       </c>
       <c r="M50" s="7" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="N50" s="7" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="51" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="51" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C51" s="6">
         <v>5006</v>
       </c>
@@ -4734,16 +5286,16 @@
         <v>5</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>57</v>
+        <v>174</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>87</v>
+        <v>175</v>
       </c>
       <c r="H51" s="6">
         <v>6</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="J51" s="6">
         <v>18</v>
@@ -4752,16 +5304,16 @@
         <v>600</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>138</v>
+        <v>215</v>
       </c>
       <c r="M51" s="7" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="N51" s="7" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="52" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="52" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C52" s="6">
         <v>5007</v>
       </c>
@@ -4772,16 +5324,16 @@
         <v>5</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>88</v>
+        <v>180</v>
       </c>
       <c r="H52" s="6">
         <v>7</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="J52" s="6">
         <v>18</v>
@@ -4790,16 +5342,16 @@
         <v>800</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>139</v>
+        <v>218</v>
       </c>
       <c r="M52" s="7" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="N52" s="7" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="53" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="53" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C53" s="6">
         <v>5008</v>
       </c>
@@ -4810,16 +5362,16 @@
         <v>5</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>59</v>
+        <v>184</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>89</v>
+        <v>185</v>
       </c>
       <c r="H53" s="6">
         <v>8</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="J53" s="6">
         <v>18</v>
@@ -4828,16 +5380,16 @@
         <v>1000</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>140</v>
+        <v>221</v>
       </c>
       <c r="M53" s="7" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="N53" s="7" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="54" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="54" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C54" s="6">
         <v>5009</v>
       </c>
@@ -4848,16 +5400,16 @@
         <v>5</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>60</v>
+        <v>189</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="H54" s="6">
         <v>9</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="J54" s="6">
         <v>18</v>
@@ -4866,16 +5418,16 @@
         <v>1200</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>141</v>
+        <v>224</v>
       </c>
       <c r="M54" s="7" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="N54" s="7" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="55" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="55" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C55" s="6">
         <v>5010</v>
       </c>
@@ -4886,16 +5438,16 @@
         <v>5</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>61</v>
+        <v>194</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>91</v>
+        <v>195</v>
       </c>
       <c r="H55" s="6">
         <v>10</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="J55" s="6">
         <v>18</v>
@@ -4904,16 +5456,16 @@
         <v>1500</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>142</v>
+        <v>227</v>
       </c>
       <c r="M55" s="7" t="s">
-        <v>203</v>
+        <v>228</v>
       </c>
       <c r="N55" s="7" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="56" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="56" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C56" s="6">
         <v>6001</v>
       </c>
@@ -4924,16 +5476,16 @@
         <v>6</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>52</v>
+        <v>148</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="H56" s="6">
         <v>1</v>
       </c>
       <c r="I56" s="8" t="s">
-        <v>30</v>
+        <v>230</v>
       </c>
       <c r="J56" s="6">
         <v>30</v>
@@ -4942,16 +5494,16 @@
         <v>100</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>144</v>
+        <v>231</v>
       </c>
       <c r="M56" s="7" t="s">
-        <v>255</v>
+        <v>232</v>
       </c>
       <c r="N56" s="7" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="57" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="57" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C57" s="6">
         <v>6002</v>
       </c>
@@ -4962,16 +5514,16 @@
         <v>6</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>53</v>
+        <v>154</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>83</v>
+        <v>155</v>
       </c>
       <c r="H57" s="6">
         <v>2</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J57" s="6">
         <v>30</v>
@@ -4980,16 +5532,16 @@
         <v>150</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>145</v>
+        <v>234</v>
       </c>
       <c r="M57" s="7" t="s">
-        <v>256</v>
+        <v>235</v>
       </c>
       <c r="N57" s="7" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="58" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="58" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C58" s="6">
         <v>6003</v>
       </c>
@@ -5000,16 +5552,16 @@
         <v>6</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>54</v>
+        <v>159</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>84</v>
+        <v>160</v>
       </c>
       <c r="H58" s="6">
         <v>3</v>
       </c>
       <c r="I58" s="8" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="J58" s="6">
         <v>30</v>
@@ -5018,16 +5570,16 @@
         <v>200</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>146</v>
+        <v>237</v>
       </c>
       <c r="M58" s="7" t="s">
-        <v>257</v>
+        <v>238</v>
       </c>
       <c r="N58" s="7" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="59" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="59" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C59" s="6">
         <v>6004</v>
       </c>
@@ -5038,16 +5590,16 @@
         <v>6</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>55</v>
+        <v>164</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>85</v>
+        <v>165</v>
       </c>
       <c r="H59" s="6">
         <v>4</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="J59" s="6">
         <v>30</v>
@@ -5056,16 +5608,16 @@
         <v>300</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>147</v>
+        <v>240</v>
       </c>
       <c r="M59" s="7" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="N59" s="7" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="60" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="60" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C60" s="6">
         <v>6005</v>
       </c>
@@ -5076,16 +5628,16 @@
         <v>6</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>56</v>
+        <v>169</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>86</v>
+        <v>170</v>
       </c>
       <c r="H60" s="6">
         <v>5</v>
       </c>
       <c r="I60" s="8" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="J60" s="6">
         <v>30</v>
@@ -5094,16 +5646,16 @@
         <v>450</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>148</v>
+        <v>243</v>
       </c>
       <c r="M60" s="7" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="N60" s="7" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="61" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="61" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C61" s="6">
         <v>6006</v>
       </c>
@@ -5114,16 +5666,16 @@
         <v>6</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>57</v>
+        <v>174</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>87</v>
+        <v>175</v>
       </c>
       <c r="H61" s="6">
         <v>6</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="J61" s="6">
         <v>30</v>
@@ -5132,16 +5684,16 @@
         <v>600</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>149</v>
+        <v>246</v>
       </c>
       <c r="M61" s="7" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="N61" s="7" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="62" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="62" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C62" s="6">
         <v>6007</v>
       </c>
@@ -5152,16 +5704,16 @@
         <v>6</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>88</v>
+        <v>180</v>
       </c>
       <c r="H62" s="6">
         <v>7</v>
       </c>
       <c r="I62" s="8" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="J62" s="6">
         <v>30</v>
@@ -5170,16 +5722,16 @@
         <v>800</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>150</v>
+        <v>249</v>
       </c>
       <c r="M62" s="7" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="N62" s="7" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="63" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="63" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C63" s="6">
         <v>6008</v>
       </c>
@@ -5190,16 +5742,16 @@
         <v>6</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>59</v>
+        <v>184</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>89</v>
+        <v>185</v>
       </c>
       <c r="H63" s="6">
         <v>8</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="J63" s="6">
         <v>30</v>
@@ -5208,16 +5760,16 @@
         <v>1000</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>151</v>
+        <v>252</v>
       </c>
       <c r="M63" s="7" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="N63" s="7" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="64" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="64" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C64" s="6">
         <v>6009</v>
       </c>
@@ -5228,16 +5780,16 @@
         <v>6</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>60</v>
+        <v>189</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="H64" s="6">
         <v>9</v>
       </c>
       <c r="I64" s="8" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="J64" s="6">
         <v>30</v>
@@ -5246,16 +5798,16 @@
         <v>1200</v>
       </c>
       <c r="L64" s="6" t="s">
-        <v>152</v>
+        <v>255</v>
       </c>
       <c r="M64" s="7" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="N64" s="7" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="65" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="65" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C65" s="6">
         <v>6010</v>
       </c>
@@ -5266,16 +5818,16 @@
         <v>6</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>61</v>
+        <v>194</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>91</v>
+        <v>195</v>
       </c>
       <c r="H65" s="6">
         <v>10</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="J65" s="6">
         <v>30</v>
@@ -5284,16 +5836,16 @@
         <v>1500</v>
       </c>
       <c r="L65" s="6" t="s">
-        <v>153</v>
+        <v>258</v>
       </c>
       <c r="M65" s="7" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="N65" s="7" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="66" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="66" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C66" s="6">
         <v>7001</v>
       </c>
@@ -5304,16 +5856,16 @@
         <v>7</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>62</v>
+        <v>261</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="H66" s="6">
         <v>1</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>26</v>
+        <v>263</v>
       </c>
       <c r="J66" s="6">
         <v>0</v>
@@ -5322,16 +5874,16 @@
         <v>100</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>93</v>
+        <v>29</v>
       </c>
       <c r="M66" s="7" t="s">
-        <v>276</v>
+        <v>30</v>
       </c>
       <c r="N66" s="7" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="67" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="67" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C67" s="6">
         <v>7002</v>
       </c>
@@ -5342,16 +5894,16 @@
         <v>7</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>63</v>
+        <v>264</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="H67" s="6">
         <v>2</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J67" s="6">
         <v>0</v>
@@ -5360,16 +5912,16 @@
         <v>150</v>
       </c>
       <c r="L67" s="6" t="s">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="M67" s="7" t="s">
-        <v>155</v>
+        <v>36</v>
       </c>
       <c r="N67" s="7" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="68" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="68" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C68" s="6">
         <v>7003</v>
       </c>
@@ -5380,16 +5932,16 @@
         <v>7</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>64</v>
+        <v>265</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="H68" s="6">
         <v>3</v>
       </c>
       <c r="I68" s="8" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="J68" s="6">
         <v>0</v>
@@ -5398,16 +5950,16 @@
         <v>200</v>
       </c>
       <c r="L68" s="6" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="M68" s="7" t="s">
-        <v>156</v>
+        <v>42</v>
       </c>
       <c r="N68" s="7" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="69" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="69" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C69" s="6">
         <v>7004</v>
       </c>
@@ -5418,16 +5970,16 @@
         <v>7</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>65</v>
+        <v>266</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="H69" s="6">
         <v>4</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="J69" s="6">
         <v>0</v>
@@ -5436,16 +5988,16 @@
         <v>300</v>
       </c>
       <c r="L69" s="6" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="M69" s="7" t="s">
-        <v>157</v>
+        <v>48</v>
       </c>
       <c r="N69" s="7" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="70" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="70" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C70" s="6">
         <v>7005</v>
       </c>
@@ -5456,16 +6008,16 @@
         <v>7</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>66</v>
+        <v>267</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="H70" s="6">
         <v>5</v>
       </c>
       <c r="I70" s="8" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="J70" s="6">
         <v>0</v>
@@ -5474,16 +6026,16 @@
         <v>450</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="M70" s="7" t="s">
-        <v>158</v>
+        <v>54</v>
       </c>
       <c r="N70" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="71" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="71" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C71" s="6">
         <v>7006</v>
       </c>
@@ -5494,16 +6046,16 @@
         <v>7</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>67</v>
+        <v>268</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="H71" s="6">
         <v>6</v>
       </c>
       <c r="I71" s="8" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="J71" s="6">
         <v>0</v>
@@ -5512,16 +6064,16 @@
         <v>600</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="M71" s="7" t="s">
-        <v>159</v>
+        <v>60</v>
       </c>
       <c r="N71" s="7" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="72" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="72" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C72" s="6">
         <v>7007</v>
       </c>
@@ -5532,16 +6084,16 @@
         <v>7</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>68</v>
+        <v>269</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="H72" s="6">
         <v>7</v>
       </c>
       <c r="I72" s="8" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="J72" s="6">
         <v>0</v>
@@ -5550,16 +6102,16 @@
         <v>800</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>99</v>
+        <v>65</v>
       </c>
       <c r="M72" s="7" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="N72" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="73" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="73" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C73" s="6">
         <v>7008</v>
       </c>
@@ -5570,16 +6122,16 @@
         <v>7</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>69</v>
+        <v>270</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="H73" s="6">
         <v>8</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="J73" s="6">
         <v>0</v>
@@ -5588,16 +6140,16 @@
         <v>1000</v>
       </c>
       <c r="L73" s="6" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="M73" s="7" t="s">
-        <v>161</v>
+        <v>72</v>
       </c>
       <c r="N73" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="74" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="74" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C74" s="6">
         <v>7009</v>
       </c>
@@ -5608,16 +6160,16 @@
         <v>7</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>70</v>
+        <v>271</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="H74" s="6">
         <v>9</v>
       </c>
       <c r="I74" s="8" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="J74" s="6">
         <v>0</v>
@@ -5626,16 +6178,16 @@
         <v>1200</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="M74" s="7" t="s">
-        <v>162</v>
+        <v>78</v>
       </c>
       <c r="N74" s="7" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="75" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="75" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C75" s="6">
         <v>7010</v>
       </c>
@@ -5646,16 +6198,16 @@
         <v>7</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>71</v>
+        <v>272</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="H75" s="6">
         <v>10</v>
       </c>
       <c r="I75" s="8" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="J75" s="6">
         <v>0</v>
@@ -5664,16 +6216,16 @@
         <v>1500</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="M75" s="7" t="s">
-        <v>163</v>
+        <v>84</v>
       </c>
       <c r="N75" s="7" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="76" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="76" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C76" s="6">
         <v>8001</v>
       </c>
@@ -5684,16 +6236,16 @@
         <v>8</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>62</v>
+        <v>261</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="H76" s="6">
         <v>1</v>
       </c>
       <c r="I76" s="6" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="J76" s="6">
         <v>0</v>
@@ -5702,16 +6254,16 @@
         <v>100</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="M76" s="7" t="s">
-        <v>164</v>
+        <v>88</v>
       </c>
       <c r="N76" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="77" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="77" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C77" s="6">
         <v>8002</v>
       </c>
@@ -5722,16 +6274,16 @@
         <v>8</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>63</v>
+        <v>264</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="H77" s="6">
         <v>2</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J77" s="6">
         <v>0</v>
@@ -5740,16 +6292,16 @@
         <v>150</v>
       </c>
       <c r="L77" s="6" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="M77" s="7" t="s">
-        <v>165</v>
+        <v>91</v>
       </c>
       <c r="N77" s="7" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="78" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="78" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C78" s="6">
         <v>8003</v>
       </c>
@@ -5760,16 +6312,16 @@
         <v>8</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>64</v>
+        <v>265</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="H78" s="6">
         <v>3</v>
       </c>
       <c r="I78" s="8" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="J78" s="6">
         <v>0</v>
@@ -5778,16 +6330,16 @@
         <v>200</v>
       </c>
       <c r="L78" s="6" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="M78" s="7" t="s">
-        <v>166</v>
+        <v>94</v>
       </c>
       <c r="N78" s="7" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="79" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="79" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C79" s="6">
         <v>8004</v>
       </c>
@@ -5798,16 +6350,16 @@
         <v>8</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>65</v>
+        <v>266</v>
       </c>
       <c r="G79" s="6" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="H79" s="6">
         <v>4</v>
       </c>
       <c r="I79" s="8" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="J79" s="6">
         <v>0</v>
@@ -5816,16 +6368,16 @@
         <v>300</v>
       </c>
       <c r="L79" s="6" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="M79" s="7" t="s">
-        <v>167</v>
+        <v>97</v>
       </c>
       <c r="N79" s="7" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="80" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="80" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C80" s="6">
         <v>8005</v>
       </c>
@@ -5836,16 +6388,16 @@
         <v>8</v>
       </c>
       <c r="F80" s="8" t="s">
-        <v>66</v>
+        <v>267</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="H80" s="6">
         <v>5</v>
       </c>
       <c r="I80" s="8" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="J80" s="6">
         <v>0</v>
@@ -5854,16 +6406,16 @@
         <v>450</v>
       </c>
       <c r="L80" s="6" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="M80" s="7" t="s">
-        <v>168</v>
+        <v>100</v>
       </c>
       <c r="N80" s="7" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="81" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="81" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C81" s="6">
         <v>8006</v>
       </c>
@@ -5874,16 +6426,16 @@
         <v>8</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>67</v>
+        <v>268</v>
       </c>
       <c r="G81" s="6" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="H81" s="6">
         <v>6</v>
       </c>
       <c r="I81" s="8" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="J81" s="6">
         <v>0</v>
@@ -5892,16 +6444,16 @@
         <v>600</v>
       </c>
       <c r="L81" s="6" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="M81" s="7" t="s">
-        <v>169</v>
+        <v>103</v>
       </c>
       <c r="N81" s="7" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="82" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="82" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C82" s="6">
         <v>8007</v>
       </c>
@@ -5912,16 +6464,16 @@
         <v>8</v>
       </c>
       <c r="F82" s="8" t="s">
-        <v>68</v>
+        <v>269</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="H82" s="6">
         <v>7</v>
       </c>
       <c r="I82" s="8" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="J82" s="6">
         <v>0</v>
@@ -5930,16 +6482,16 @@
         <v>800</v>
       </c>
       <c r="L82" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="M82" s="7" t="s">
-        <v>170</v>
+        <v>106</v>
       </c>
       <c r="N82" s="7" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="83" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="83" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C83" s="6">
         <v>8008</v>
       </c>
@@ -5950,16 +6502,16 @@
         <v>8</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>69</v>
+        <v>270</v>
       </c>
       <c r="G83" s="6" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="H83" s="6">
         <v>8</v>
       </c>
       <c r="I83" s="8" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="J83" s="6">
         <v>0</v>
@@ -5968,16 +6520,16 @@
         <v>1000</v>
       </c>
       <c r="L83" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="M83" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="N83" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="M83" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="N83" s="7" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="84" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="84" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C84" s="6">
         <v>8009</v>
       </c>
@@ -5988,16 +6540,16 @@
         <v>8</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>70</v>
+        <v>271</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="H84" s="6">
         <v>9</v>
       </c>
       <c r="I84" s="8" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="J84" s="6">
         <v>0</v>
@@ -6009,13 +6561,13 @@
         <v>111</v>
       </c>
       <c r="M84" s="7" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
       <c r="N84" s="7" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="85" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="85" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C85" s="6">
         <v>8010</v>
       </c>
@@ -6026,16 +6578,16 @@
         <v>8</v>
       </c>
       <c r="F85" s="8" t="s">
-        <v>71</v>
+        <v>272</v>
       </c>
       <c r="G85" s="6" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="H85" s="6">
         <v>10</v>
       </c>
       <c r="I85" s="8" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="J85" s="6">
         <v>0</v>
@@ -6044,16 +6596,16 @@
         <v>1500</v>
       </c>
       <c r="L85" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M85" s="7" t="s">
-        <v>173</v>
+        <v>115</v>
       </c>
       <c r="N85" s="7" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="86" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="86" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C86" s="6">
         <v>9001</v>
       </c>
@@ -6064,16 +6616,16 @@
         <v>9</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>62</v>
+        <v>261</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="H86" s="6">
         <v>1</v>
       </c>
       <c r="I86" s="6" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="J86" s="6">
         <v>0</v>
@@ -6082,16 +6634,16 @@
         <v>100</v>
       </c>
       <c r="L86" s="6" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="M86" s="7" t="s">
-        <v>174</v>
+        <v>119</v>
       </c>
       <c r="N86" s="7" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="87" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="87" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C87" s="6">
         <v>9002</v>
       </c>
@@ -6102,16 +6654,16 @@
         <v>9</v>
       </c>
       <c r="F87" s="8" t="s">
-        <v>63</v>
+        <v>264</v>
       </c>
       <c r="G87" s="6" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="H87" s="6">
         <v>2</v>
       </c>
       <c r="I87" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J87" s="6">
         <v>0</v>
@@ -6120,16 +6672,16 @@
         <v>150</v>
       </c>
       <c r="L87" s="6" t="s">
-        <v>143</v>
+        <v>275</v>
       </c>
       <c r="M87" s="7" t="s">
-        <v>175</v>
+        <v>122</v>
       </c>
       <c r="N87" s="7" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="88" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="88" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C88" s="6">
         <v>9003</v>
       </c>
@@ -6140,16 +6692,16 @@
         <v>9</v>
       </c>
       <c r="F88" s="8" t="s">
-        <v>64</v>
+        <v>265</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="H88" s="6">
         <v>3</v>
       </c>
       <c r="I88" s="8" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="J88" s="6">
         <v>0</v>
@@ -6158,16 +6710,16 @@
         <v>200</v>
       </c>
       <c r="L88" s="6" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="M88" s="7" t="s">
-        <v>176</v>
+        <v>125</v>
       </c>
       <c r="N88" s="7" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="89" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="89" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C89" s="6">
         <v>9004</v>
       </c>
@@ -6178,16 +6730,16 @@
         <v>9</v>
       </c>
       <c r="F89" s="8" t="s">
-        <v>65</v>
+        <v>266</v>
       </c>
       <c r="G89" s="6" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="H89" s="6">
         <v>4</v>
       </c>
       <c r="I89" s="8" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="J89" s="6">
         <v>0</v>
@@ -6196,16 +6748,16 @@
         <v>300</v>
       </c>
       <c r="L89" s="6" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="M89" s="7" t="s">
-        <v>177</v>
+        <v>128</v>
       </c>
       <c r="N89" s="7" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="90" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="90" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C90" s="6">
         <v>9005</v>
       </c>
@@ -6216,16 +6768,16 @@
         <v>9</v>
       </c>
       <c r="F90" s="8" t="s">
-        <v>66</v>
+        <v>267</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="H90" s="6">
         <v>5</v>
       </c>
       <c r="I90" s="8" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="J90" s="6">
         <v>0</v>
@@ -6234,16 +6786,16 @@
         <v>450</v>
       </c>
       <c r="L90" s="6" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="M90" s="7" t="s">
-        <v>178</v>
+        <v>131</v>
       </c>
       <c r="N90" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="91" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="91" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C91" s="6">
         <v>9006</v>
       </c>
@@ -6254,16 +6806,16 @@
         <v>9</v>
       </c>
       <c r="F91" s="8" t="s">
-        <v>67</v>
+        <v>268</v>
       </c>
       <c r="G91" s="6" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="H91" s="6">
         <v>6</v>
       </c>
       <c r="I91" s="8" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="J91" s="6">
         <v>0</v>
@@ -6272,16 +6824,16 @@
         <v>600</v>
       </c>
       <c r="L91" s="6" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="M91" s="7" t="s">
-        <v>179</v>
+        <v>134</v>
       </c>
       <c r="N91" s="7" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="92" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="92" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C92" s="6">
         <v>9007</v>
       </c>
@@ -6292,16 +6844,16 @@
         <v>9</v>
       </c>
       <c r="F92" s="8" t="s">
-        <v>68</v>
+        <v>269</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="H92" s="6">
         <v>7</v>
       </c>
       <c r="I92" s="8" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="J92" s="6">
         <v>0</v>
@@ -6310,16 +6862,16 @@
         <v>800</v>
       </c>
       <c r="L92" s="6" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="M92" s="7" t="s">
-        <v>180</v>
+        <v>137</v>
       </c>
       <c r="N92" s="7" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="93" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="93" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C93" s="6">
         <v>9008</v>
       </c>
@@ -6330,16 +6882,16 @@
         <v>9</v>
       </c>
       <c r="F93" s="8" t="s">
-        <v>69</v>
+        <v>270</v>
       </c>
       <c r="G93" s="6" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="H93" s="6">
         <v>8</v>
       </c>
       <c r="I93" s="8" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="J93" s="6">
         <v>0</v>
@@ -6348,16 +6900,16 @@
         <v>1000</v>
       </c>
       <c r="L93" s="6" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="M93" s="7" t="s">
-        <v>181</v>
+        <v>140</v>
       </c>
       <c r="N93" s="7" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="94" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="94" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C94" s="6">
         <v>9009</v>
       </c>
@@ -6368,16 +6920,16 @@
         <v>9</v>
       </c>
       <c r="F94" s="8" t="s">
-        <v>70</v>
+        <v>271</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="H94" s="6">
         <v>9</v>
       </c>
       <c r="I94" s="8" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="J94" s="6">
         <v>0</v>
@@ -6386,16 +6938,16 @@
         <v>1200</v>
       </c>
       <c r="L94" s="6" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="M94" s="7" t="s">
-        <v>182</v>
+        <v>143</v>
       </c>
       <c r="N94" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="95" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="95" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C95" s="6">
         <v>9010</v>
       </c>
@@ -6406,16 +6958,16 @@
         <v>9</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>71</v>
+        <v>272</v>
       </c>
       <c r="G95" s="6" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="H95" s="6">
         <v>10</v>
       </c>
       <c r="I95" s="8" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="J95" s="6">
         <v>0</v>
@@ -6424,19 +6976,19 @@
         <v>1500</v>
       </c>
       <c r="L95" s="6" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="M95" s="7" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="N95" s="7" t="s">
-        <v>233</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
